--- a/data/1FEB_25_26/clutch_aggregated_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/clutch_aggregated_25_26_1FEB.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W233"/>
+  <dimension ref="A1:W236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>21.35</v>
+        <v>22.52</v>
       </c>
       <c r="E2" t="n">
-        <v>1281</v>
+        <v>1351.2</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -611,13 +611,13 @@
         <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>15.72128337236534</v>
+        <v>14.9045026642984</v>
       </c>
       <c r="V2" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="W2" t="n">
-        <v>6.506323185011708</v>
+        <v>-0.6147957371225573</v>
       </c>
     </row>
     <row r="3">
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>15.94</v>
+        <v>19.81</v>
       </c>
       <c r="E4" t="n">
-        <v>956.4</v>
+        <v>1188.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -731,10 +731,10 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" t="n">
         <v>0.375</v>
@@ -752,22 +752,22 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>22.140382685069</v>
+        <v>20.16330641090358</v>
       </c>
       <c r="V4" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="W4" t="n">
-        <v>-2.49400878293601</v>
+        <v>-7.023528520949016</v>
       </c>
     </row>
     <row r="5">
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>10.92</v>
+        <v>14.14</v>
       </c>
       <c r="E5" t="n">
-        <v>655.2</v>
+        <v>848.4000000000001</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -827,22 +827,22 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>11.93914835164835</v>
+        <v>9.220332390381895</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W5" t="n">
-        <v>-6.160173992673989</v>
+        <v>-8.316669024045259</v>
       </c>
     </row>
     <row r="6">
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>37.8</v>
+        <v>40.17</v>
       </c>
       <c r="E7" t="n">
-        <v>2268</v>
+        <v>2410.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -986,13 +986,13 @@
         <v>8</v>
       </c>
       <c r="U7" t="n">
-        <v>21.5888253968254</v>
+        <v>20.31510082150859</v>
       </c>
       <c r="V7" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="W7" t="n">
-        <v>6.437865079365081</v>
+        <v>5.355354742345035</v>
       </c>
     </row>
     <row r="8">
@@ -1007,19 +1007,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>46.12</v>
+        <v>50.5</v>
       </c>
       <c r="E8" t="n">
-        <v>2767.2</v>
+        <v>3030</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H8" t="n">
         <v>6</v>
@@ -1031,13 +1031,13 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3684210526315789</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1046,10 +1046,10 @@
         <v>9</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -1061,13 +1061,13 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>31.17455117085862</v>
+        <v>33.09962178217821</v>
       </c>
       <c r="V8" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="W8" t="n">
-        <v>-3.972959670424979</v>
+        <v>-7.104619801980198</v>
       </c>
     </row>
     <row r="9">
@@ -1157,25 +1157,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88</v>
+        <v>36.41</v>
       </c>
       <c r="E10" t="n">
-        <v>2032.8</v>
+        <v>2184.6</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -1187,7 +1187,7 @@
         <v>16</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.32</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1196,7 +1196,7 @@
         <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1211,13 +1211,13 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>63.20512396694216</v>
+        <v>62.35842351002474</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="W10" t="n">
-        <v>5.637910271546634</v>
+        <v>-0.9339686899203524</v>
       </c>
     </row>
     <row r="11">
@@ -1382,25 +1382,25 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>40.51</v>
+        <v>44.89</v>
       </c>
       <c r="E13" t="n">
-        <v>2430.6</v>
+        <v>2693.4</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
         <v>7</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
         <v>4</v>
@@ -1412,7 +1412,7 @@
         <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.75</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>26.60247840039497</v>
+        <v>25.17963911784362</v>
       </c>
       <c r="V13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>12.15649716119476</v>
+        <v>7.059685898863886</v>
       </c>
     </row>
     <row r="14">
@@ -1457,13 +1457,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>31.43</v>
+        <v>31.61</v>
       </c>
       <c r="E14" t="n">
-        <v>1885.8</v>
+        <v>1896.6</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -1511,13 +1511,13 @@
         <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>10.01130766783328</v>
+        <v>9.954299272382158</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
-        <v>26.23784282532612</v>
+        <v>26.0884340398608</v>
       </c>
     </row>
     <row r="15">
@@ -1532,13 +1532,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>6.050000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="E15" t="n">
-        <v>363</v>
+        <v>465</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -1556,10 +1556,10 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>14.80135537190083</v>
+        <v>21.8226064516129</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="W15" t="n">
-        <v>65.66624793388431</v>
+        <v>83.3097806451613</v>
       </c>
     </row>
     <row r="16">
@@ -1607,29 +1607,29 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>37.34</v>
+        <v>40.32</v>
       </c>
       <c r="E16" t="n">
-        <v>2240.4</v>
+        <v>2419.2</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
+        <v>9</v>
+      </c>
+      <c r="I16" t="n">
+        <v>16</v>
+      </c>
+      <c r="J16" t="n">
         <v>8</v>
       </c>
-      <c r="I16" t="n">
-        <v>14</v>
-      </c>
-      <c r="J16" t="n">
-        <v>7</v>
-      </c>
       <c r="K16" t="n">
         <v>2</v>
       </c>
@@ -1637,7 +1637,7 @@
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.65</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1652,22 +1652,22 @@
         <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>41.43754686663097</v>
+        <v>40.83832837301588</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="W16" t="n">
-        <v>15.40115693626139</v>
+        <v>3.016185515873016</v>
       </c>
     </row>
     <row r="17">
@@ -1832,13 +1832,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>20.47</v>
+        <v>22.1</v>
       </c>
       <c r="E19" t="n">
-        <v>1228.2</v>
+        <v>1326</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1886,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>59.54822667318026</v>
+        <v>55.15620814479638</v>
       </c>
       <c r="V19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W19" t="n">
-        <v>55.73747435271129</v>
+        <v>44.33503619909502</v>
       </c>
     </row>
     <row r="20">
@@ -1907,28 +1907,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>17.16</v>
+        <v>18.96</v>
       </c>
       <c r="E20" t="n">
-        <v>1029.6</v>
+        <v>1137.6</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
         <v>3</v>
@@ -1952,22 +1952,22 @@
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>10.4763986013986</v>
+        <v>14.37579113924051</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>40.34800116550117</v>
+        <v>35.98584915611814</v>
       </c>
     </row>
     <row r="21">
@@ -1982,13 +1982,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>28.8</v>
+        <v>30.23</v>
       </c>
       <c r="E21" t="n">
-        <v>1728</v>
+        <v>1813.8</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -2036,13 +2036,13 @@
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>20.81902083333333</v>
+        <v>19.83419781673834</v>
       </c>
       <c r="V21" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="W21" t="n">
-        <v>14.14373263888889</v>
+        <v>9.597641415812106</v>
       </c>
     </row>
     <row r="22">
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22" t="n">
-        <v>26.75</v>
+        <v>30</v>
       </c>
       <c r="E22" t="n">
-        <v>1605</v>
+        <v>1800</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2102,22 +2102,22 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>28.72844485981308</v>
+        <v>25.61619666666666</v>
       </c>
       <c r="V22" t="n">
         <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>21.2693906542056</v>
+        <v>16.01095666666667</v>
       </c>
     </row>
     <row r="23">
@@ -2132,13 +2132,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>28.7</v>
       </c>
       <c r="E23" t="n">
-        <v>1560</v>
+        <v>1722</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2177,22 +2177,22 @@
         <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T23" t="n">
         <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>13.50062307692308</v>
+        <v>12.23052961672474</v>
       </c>
       <c r="V23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>15.47838461538461</v>
+        <v>6.018188153310102</v>
       </c>
     </row>
     <row r="24">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>24.16</v>
+        <v>27.39</v>
       </c>
       <c r="E24" t="n">
-        <v>1449.6</v>
+        <v>1643.4</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2261,13 +2261,13 @@
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>22.47769039735099</v>
+        <v>19.82698064987222</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="W24" t="n">
-        <v>12.06540149006622</v>
+        <v>7.366582694414019</v>
       </c>
     </row>
     <row r="25">
@@ -2282,25 +2282,25 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>33.5</v>
       </c>
       <c r="E25" t="n">
-        <v>1740</v>
+        <v>2010</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
         <v>15</v>
-      </c>
-      <c r="H25" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" t="n">
-        <v>11</v>
       </c>
       <c r="J25" t="n">
         <v>5</v>
@@ -2312,7 +2312,7 @@
         <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5</v>
+        <v>0.425</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2321,7 +2321,7 @@
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q25" t="n">
         <v>2</v>
@@ -2336,13 +2336,13 @@
         <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>51.14338275862069</v>
+        <v>54.50113731343284</v>
       </c>
       <c r="V25" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>19.8064448275862</v>
+        <v>9.266176119402983</v>
       </c>
     </row>
     <row r="26">
@@ -4157,19 +4157,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>6.92</v>
+        <v>7.79</v>
       </c>
       <c r="E50" t="n">
-        <v>415.2</v>
+        <v>467.4</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -4211,13 +4211,13 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>16.81377167630058</v>
+        <v>26.10414634146341</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="W50" t="n">
-        <v>-8.467023121387284</v>
+        <v>-19.40210526315789</v>
       </c>
     </row>
     <row r="51">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D53" t="n">
-        <v>22.7</v>
+        <v>24.67</v>
       </c>
       <c r="E53" t="n">
-        <v>1362</v>
+        <v>1480.2</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -4427,22 +4427,22 @@
         <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S53" t="n">
         <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>14.69818061674009</v>
+        <v>13.52447101743008</v>
       </c>
       <c r="V53" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="W53" t="n">
-        <v>-0.7331277533039651</v>
+        <v>-21.91257397648966</v>
       </c>
     </row>
     <row r="54">
@@ -4532,13 +4532,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D55" t="n">
-        <v>42.29</v>
+        <v>46.84</v>
       </c>
       <c r="E55" t="n">
-        <v>2537.4</v>
+        <v>2810.4</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
+        <v>17</v>
+      </c>
+      <c r="L55" t="n">
         <v>15</v>
-      </c>
-      <c r="L55" t="n">
-        <v>14</v>
       </c>
       <c r="M55" t="n">
         <v>0.4166666666666667</v>
@@ -4586,13 +4586,13 @@
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>34.77794514069519</v>
+        <v>33.15106319385141</v>
       </c>
       <c r="V55" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="W55" t="n">
-        <v>35.56459919602743</v>
+        <v>27.11984201537148</v>
       </c>
     </row>
     <row r="56">
@@ -4607,19 +4607,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D56" t="n">
-        <v>45.01</v>
+        <v>48.89</v>
       </c>
       <c r="E56" t="n">
-        <v>2700.6</v>
+        <v>2933.4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H56" t="n">
         <v>10</v>
@@ -4637,37 +4637,37 @@
         <v>5</v>
       </c>
       <c r="M56" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P56" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q56" t="n">
         <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T56" t="n">
         <v>4</v>
       </c>
       <c r="U56" t="n">
-        <v>35.16406798489225</v>
+        <v>36.4224238085498</v>
       </c>
       <c r="V56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W56" t="n">
-        <v>15.6892112863808</v>
+        <v>6.34600531806095</v>
       </c>
     </row>
     <row r="57">
@@ -4757,13 +4757,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>13.79</v>
+        <v>17.57</v>
       </c>
       <c r="E58" t="n">
-        <v>827.4</v>
+        <v>1054.2</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -4811,13 +4811,13 @@
         <v>3</v>
       </c>
       <c r="U58" t="n">
-        <v>29.06717186366933</v>
+        <v>22.81367672168469</v>
       </c>
       <c r="V58" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="W58" t="n">
-        <v>44.95255257432922</v>
+        <v>18.49415480933409</v>
       </c>
     </row>
     <row r="59">
@@ -4832,28 +4832,28 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D59" t="n">
-        <v>42.16</v>
+        <v>46.81</v>
       </c>
       <c r="E59" t="n">
-        <v>2529.6</v>
+        <v>2808.6</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.46875</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -4877,22 +4877,22 @@
         <v>2</v>
       </c>
       <c r="R59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T59" t="n">
         <v>2</v>
       </c>
       <c r="U59" t="n">
-        <v>19.04953510436432</v>
+        <v>20.53567400128177</v>
       </c>
       <c r="V59" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="W59" t="n">
-        <v>24.36089658444022</v>
+        <v>14.2601452681051</v>
       </c>
     </row>
     <row r="60">
@@ -4982,13 +4982,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>14.4</v>
+        <v>17.95</v>
       </c>
       <c r="E61" t="n">
-        <v>864</v>
+        <v>1077</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -5027,22 +5027,22 @@
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" t="n">
         <v>3</v>
       </c>
       <c r="U61" t="n">
-        <v>13.31791666666667</v>
+        <v>10.68401114206128</v>
       </c>
       <c r="V61" t="n">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="W61" t="n">
-        <v>-21.72454166666667</v>
+        <v>-21.33996657381616</v>
       </c>
     </row>
     <row r="62">
@@ -5057,13 +5057,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62" t="n">
-        <v>1.03</v>
+        <v>1.35</v>
       </c>
       <c r="E62" t="n">
-        <v>61.8</v>
+        <v>81</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -5114,10 +5114,10 @@
         <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="W62" t="n">
-        <v>-63.57</v>
+        <v>-48.50155555555556</v>
       </c>
     </row>
     <row r="63">
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D64" t="n">
-        <v>16.59</v>
+        <v>17.44</v>
       </c>
       <c r="E64" t="n">
-        <v>995.4</v>
+        <v>1046.4</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -5261,13 +5261,13 @@
         <v>4</v>
       </c>
       <c r="U64" t="n">
-        <v>27.691742013261</v>
+        <v>26.3420871559633</v>
       </c>
       <c r="V64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W64" t="n">
-        <v>88.93463532248342</v>
+        <v>79.72623853211009</v>
       </c>
     </row>
     <row r="65">
@@ -5357,25 +5357,25 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D66" t="n">
-        <v>25.57</v>
+        <v>26.35</v>
       </c>
       <c r="E66" t="n">
-        <v>1534.2</v>
+        <v>1581</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H66" t="n">
         <v>5</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J66" t="n">
         <v>3</v>
@@ -5387,13 +5387,13 @@
         <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>1.083333333333333</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P66" t="n">
         <v>1</v>
@@ -5411,13 +5411,13 @@
         <v>4</v>
       </c>
       <c r="U66" t="n">
-        <v>17.44796245600313</v>
+        <v>18.41155218216319</v>
       </c>
       <c r="V66" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W66" t="n">
-        <v>97.59965584669534</v>
+        <v>93.23048197343454</v>
       </c>
     </row>
     <row r="67">
@@ -5432,28 +5432,28 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D67" t="n">
-        <v>16.36</v>
+        <v>17.21</v>
       </c>
       <c r="E67" t="n">
-        <v>981.6</v>
+        <v>1032.6</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
         <v>2</v>
@@ -5462,7 +5462,7 @@
         <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.625</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -5486,13 +5486,13 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>14.34826405867971</v>
+        <v>15.28576990122022</v>
       </c>
       <c r="V67" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="W67" t="n">
-        <v>-15.47046454767726</v>
+        <v>-19.64536897152819</v>
       </c>
     </row>
     <row r="68">
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D69" t="n">
-        <v>12.27</v>
+        <v>12.44</v>
       </c>
       <c r="E69" t="n">
-        <v>736.1999999999999</v>
+        <v>746.4</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -5636,13 +5636,13 @@
         <v>3</v>
       </c>
       <c r="U69" t="n">
-        <v>15.61312958435208</v>
+        <v>15.39976688102894</v>
       </c>
       <c r="V69" t="n">
         <v>10</v>
       </c>
       <c r="W69" t="n">
-        <v>25.11427872860636</v>
+        <v>24.771077170418</v>
       </c>
     </row>
     <row r="70">
@@ -5732,13 +5732,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D71" t="n">
-        <v>26.57</v>
+        <v>27.42</v>
       </c>
       <c r="E71" t="n">
-        <v>1594.2</v>
+        <v>1645.2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -5786,13 +5786,13 @@
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>40.51244260444109</v>
+        <v>39.25658643326039</v>
       </c>
       <c r="V71" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W71" t="n">
-        <v>72.35809183289425</v>
+        <v>67.0151167031364</v>
       </c>
     </row>
     <row r="72">
@@ -6032,13 +6032,13 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D75" t="n">
-        <v>21.45</v>
+        <v>21.88</v>
       </c>
       <c r="E75" t="n">
-        <v>1287</v>
+        <v>1312.8</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>47.95034965034965</v>
+        <v>48.97326325411335</v>
       </c>
       <c r="V75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>32.90601864801865</v>
+        <v>28.32879798903108</v>
       </c>
     </row>
     <row r="76">
@@ -6707,25 +6707,25 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" t="n">
-        <v>12.96</v>
+        <v>13.08</v>
       </c>
       <c r="E84" t="n">
-        <v>777.6</v>
+        <v>784.8</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H84" t="n">
         <v>4</v>
       </c>
       <c r="I84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
         <v>1</v>
@@ -6737,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5625</v>
       </c>
       <c r="N84" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>2</v>
       </c>
       <c r="Q84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -6761,13 +6761,13 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>36.65683641975309</v>
+        <v>36.80851681957187</v>
       </c>
       <c r="V84" t="n">
         <v>2</v>
       </c>
       <c r="W84" t="n">
-        <v>13.1692361111111</v>
+        <v>13.04841743119265</v>
       </c>
     </row>
     <row r="85">
@@ -6782,13 +6782,13 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D85" t="n">
-        <v>32.17</v>
+        <v>32.29</v>
       </c>
       <c r="E85" t="n">
-        <v>1930.2</v>
+        <v>1937.4</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>7</v>
       </c>
       <c r="U85" t="n">
-        <v>20.55859185576624</v>
+        <v>20.48218953236296</v>
       </c>
       <c r="V85" t="n">
         <v>12</v>
       </c>
       <c r="W85" t="n">
-        <v>4.063434877214796</v>
+        <v>4.048333849489006</v>
       </c>
     </row>
     <row r="86">
@@ -6857,13 +6857,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D86" t="n">
-        <v>13.91</v>
+        <v>14.03</v>
       </c>
       <c r="E86" t="n">
-        <v>834.6</v>
+        <v>841.8000000000001</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>3</v>
       </c>
       <c r="K86" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L86" t="n">
         <v>6</v>
@@ -6902,22 +6902,22 @@
         <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S86" t="n">
         <v>1</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>30.94772106398275</v>
+        <v>31.08339272986458</v>
       </c>
       <c r="V86" t="n">
         <v>6</v>
       </c>
       <c r="W86" t="n">
-        <v>12.92736161035227</v>
+        <v>12.81679258731291</v>
       </c>
     </row>
     <row r="87">
@@ -6932,13 +6932,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D87" t="n">
-        <v>22.83</v>
+        <v>22.95</v>
       </c>
       <c r="E87" t="n">
-        <v>1369.8</v>
+        <v>1377</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -6986,13 +6986,13 @@
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>19.77263250109505</v>
+        <v>19.66924618736383</v>
       </c>
       <c r="V87" t="n">
         <v>-1</v>
       </c>
       <c r="W87" t="n">
-        <v>13.41864651773981</v>
+        <v>13.34848366013072</v>
       </c>
     </row>
     <row r="88">
@@ -7007,13 +7007,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D88" t="n">
-        <v>39.91</v>
+        <v>40.03</v>
       </c>
       <c r="E88" t="n">
-        <v>2394.6</v>
+        <v>2401.8</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -7061,13 +7061,13 @@
         <v>2</v>
       </c>
       <c r="U88" t="n">
-        <v>51.56563267351541</v>
+        <v>51.41105171121659</v>
       </c>
       <c r="V88" t="n">
         <v>-10</v>
       </c>
       <c r="W88" t="n">
-        <v>-19.78645702831371</v>
+        <v>-19.72714214339246</v>
       </c>
     </row>
     <row r="89">
@@ -7232,25 +7232,25 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D91" t="n">
-        <v>29.21</v>
+        <v>33.86</v>
       </c>
       <c r="E91" t="n">
-        <v>1752.6</v>
+        <v>2031.6</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
+        <v>7</v>
+      </c>
+      <c r="H91" t="n">
         <v>5</v>
       </c>
-      <c r="H91" t="n">
-        <v>4</v>
-      </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>1</v>
@@ -7262,7 +7262,7 @@
         <v>2</v>
       </c>
       <c r="M91" t="n">
-        <v>0.9</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -7274,25 +7274,25 @@
         <v>1</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S91" t="n">
         <v>2</v>
       </c>
       <c r="T91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U91" t="n">
-        <v>12.41156795617939</v>
+        <v>14.69927347903131</v>
       </c>
       <c r="V91" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="W91" t="n">
-        <v>21.65614515576857</v>
+        <v>29.30047253396338</v>
       </c>
     </row>
     <row r="92">
@@ -7457,37 +7457,37 @@
         </is>
       </c>
       <c r="C94" t="n">
+        <v>8</v>
+      </c>
+      <c r="D94" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1309.8</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
         <v>7</v>
       </c>
-      <c r="D94" t="n">
-        <v>17.18</v>
-      </c>
-      <c r="E94" t="n">
-        <v>1030.8</v>
-      </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" t="n">
+        <v>3</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
+        <v>6</v>
+      </c>
+      <c r="L94" t="n">
         <v>5</v>
       </c>
-      <c r="H94" t="n">
-        <v>3</v>
-      </c>
-      <c r="I94" t="n">
-        <v>2</v>
-      </c>
-      <c r="J94" t="n">
-        <v>1</v>
-      </c>
-      <c r="K94" t="n">
-        <v>4</v>
-      </c>
-      <c r="L94" t="n">
-        <v>3</v>
-      </c>
       <c r="M94" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N94" t="n">
         <v>0</v>
@@ -7499,7 +7499,7 @@
         <v>2</v>
       </c>
       <c r="Q94" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -7511,13 +7511,13 @@
         <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>37.99214784633294</v>
+        <v>38.81603756298671</v>
       </c>
       <c r="V94" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="W94" t="n">
-        <v>26.15625727590222</v>
+        <v>37.05462666055886</v>
       </c>
     </row>
     <row r="95">
@@ -7532,13 +7532,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D95" t="n">
-        <v>4.359999999999999</v>
+        <v>4.93</v>
       </c>
       <c r="E95" t="n">
-        <v>261.6</v>
+        <v>295.8</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
@@ -7586,13 +7586,13 @@
         <v>3</v>
       </c>
       <c r="U95" t="n">
-        <v>33.57337155963302</v>
+        <v>29.69166328600405</v>
       </c>
       <c r="V95" t="n">
         <v>-3</v>
       </c>
       <c r="W95" t="n">
-        <v>-34.22419724770641</v>
+        <v>-30.26724137931034</v>
       </c>
     </row>
     <row r="96">
@@ -7682,13 +7682,13 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D97" t="n">
-        <v>19.64</v>
+        <v>20.31</v>
       </c>
       <c r="E97" t="n">
-        <v>1178.4</v>
+        <v>1218.6</v>
       </c>
       <c r="F97" t="n">
         <v>0</v>
@@ -7736,13 +7736,13 @@
         <v>3</v>
       </c>
       <c r="U97" t="n">
-        <v>32.18612016293279</v>
+        <v>31.12434268833087</v>
       </c>
       <c r="V97" t="n">
         <v>15</v>
       </c>
       <c r="W97" t="n">
-        <v>43.21553462321793</v>
+        <v>41.78991137370755</v>
       </c>
     </row>
     <row r="98">
@@ -7832,13 +7832,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D99" t="n">
-        <v>6.76</v>
+        <v>7.33</v>
       </c>
       <c r="E99" t="n">
-        <v>405.6</v>
+        <v>439.8</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -7886,13 +7886,13 @@
         <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>33.71147928994083</v>
+        <v>31.0899863574352</v>
       </c>
       <c r="V99" t="n">
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>20.94991124260355</v>
+        <v>19.32079126875853</v>
       </c>
     </row>
     <row r="100">
@@ -7907,28 +7907,28 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D100" t="n">
-        <v>32.44</v>
+        <v>36.52</v>
       </c>
       <c r="E100" t="n">
-        <v>1946.4</v>
+        <v>2191.2</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H100" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I100" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K100" t="n">
         <v>8</v>
@@ -7937,7 +7937,7 @@
         <v>5</v>
       </c>
       <c r="M100" t="n">
-        <v>0.3695652173913043</v>
+        <v>0.4</v>
       </c>
       <c r="N100" t="n">
         <v>0</v>
@@ -7952,22 +7952,22 @@
         <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T100" t="n">
         <v>2</v>
       </c>
       <c r="U100" t="n">
-        <v>54.85942971639951</v>
+        <v>52.53013964950713</v>
       </c>
       <c r="V100" t="n">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="W100" t="n">
-        <v>-9.597401356350181</v>
+        <v>2.87468510405258</v>
       </c>
     </row>
     <row r="101">
@@ -8057,28 +8057,28 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D102" t="n">
-        <v>22.42</v>
+        <v>26.5</v>
       </c>
       <c r="E102" t="n">
-        <v>1345.2</v>
+        <v>1590</v>
       </c>
       <c r="F102" t="n">
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K102" t="n">
         <v>4</v>
@@ -8087,7 +8087,7 @@
         <v>4</v>
       </c>
       <c r="M102" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="N102" t="n">
         <v>0</v>
@@ -8111,13 +8111,13 @@
         <v>2</v>
       </c>
       <c r="U102" t="n">
-        <v>22.54544157002676</v>
+        <v>21.69319245283019</v>
       </c>
       <c r="V102" t="n">
-        <v>-38</v>
+        <v>-32</v>
       </c>
       <c r="W102" t="n">
-        <v>-79.4250535236396</v>
+        <v>-51.48628301886792</v>
       </c>
     </row>
     <row r="103">
@@ -8282,13 +8282,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D105" t="n">
-        <v>23.71</v>
+        <v>27.69</v>
       </c>
       <c r="E105" t="n">
-        <v>1422.6</v>
+        <v>1661.4</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -8318,7 +8318,7 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P105" t="n">
         <v>3</v>
@@ -8327,22 +8327,22 @@
         <v>1</v>
       </c>
       <c r="R105" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U105" t="n">
-        <v>39.99724167018136</v>
+        <v>34.24827013362225</v>
       </c>
       <c r="V105" t="n">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="W105" t="n">
-        <v>-14.37078869675243</v>
+        <v>5.366905019862767</v>
       </c>
     </row>
     <row r="106">
@@ -9332,37 +9332,37 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D119" t="n">
-        <v>26.3</v>
+        <v>30.82</v>
       </c>
       <c r="E119" t="n">
-        <v>1578</v>
+        <v>1849.2</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
       </c>
       <c r="G119" t="n">
+        <v>7</v>
+      </c>
+      <c r="H119" t="n">
+        <v>3</v>
+      </c>
+      <c r="I119" t="n">
         <v>5</v>
       </c>
-      <c r="H119" t="n">
-        <v>3</v>
-      </c>
-      <c r="I119" t="n">
-        <v>3</v>
-      </c>
       <c r="J119" t="n">
         <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M119" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
@@ -9377,22 +9377,22 @@
         <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S119" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T119" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U119" t="n">
-        <v>13.85544866920152</v>
+        <v>16.6455515898767</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>-26.90617870722433</v>
+        <v>-22.64779039584685</v>
       </c>
     </row>
     <row r="120">
@@ -9407,25 +9407,25 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D120" t="n">
-        <v>28.16</v>
+        <v>32.18</v>
       </c>
       <c r="E120" t="n">
-        <v>1689.6</v>
+        <v>1930.8</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H120" t="n">
         <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -9437,7 +9437,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
@@ -9461,13 +9461,13 @@
         <v>2</v>
       </c>
       <c r="U120" t="n">
-        <v>10.30640980113636</v>
+        <v>10.6291578620261</v>
       </c>
       <c r="V120" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="W120" t="n">
-        <v>-11.80013849431818</v>
+        <v>-13.53154443753884</v>
       </c>
     </row>
     <row r="121">
@@ -9482,13 +9482,13 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D121" t="n">
-        <v>25.36</v>
+        <v>25.94</v>
       </c>
       <c r="E121" t="n">
-        <v>1521.6</v>
+        <v>1556.4</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>4</v>
       </c>
       <c r="U121" t="n">
-        <v>19.95083990536277</v>
+        <v>19.5047532767926</v>
       </c>
       <c r="V121" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="W121" t="n">
-        <v>-12.88742902208202</v>
+        <v>-13.78856592135697</v>
       </c>
     </row>
     <row r="122">
@@ -9632,25 +9632,25 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D123" t="n">
-        <v>28.84</v>
+        <v>31.87</v>
       </c>
       <c r="E123" t="n">
-        <v>1730.4</v>
+        <v>1912.2</v>
       </c>
       <c r="F123" t="n">
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H123" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I123" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J123" t="n">
         <v>2</v>
@@ -9662,7 +9662,7 @@
         <v>10</v>
       </c>
       <c r="M123" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4375</v>
       </c>
       <c r="N123" t="n">
         <v>0</v>
@@ -9671,28 +9671,28 @@
         <v>2</v>
       </c>
       <c r="P123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
       </c>
       <c r="R123" t="n">
+        <v>7</v>
+      </c>
+      <c r="S123" t="n">
         <v>5</v>
       </c>
-      <c r="S123" t="n">
-        <v>4</v>
-      </c>
       <c r="T123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U123" t="n">
-        <v>46.40993758668517</v>
+        <v>46.82351427674931</v>
       </c>
       <c r="V123" t="n">
         <v>0</v>
       </c>
       <c r="W123" t="n">
-        <v>-6.956158113730929</v>
+        <v>-6.294810166300596</v>
       </c>
     </row>
     <row r="124">
@@ -9707,13 +9707,13 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D124" t="n">
-        <v>15.62</v>
+        <v>17.57</v>
       </c>
       <c r="E124" t="n">
-        <v>937.2</v>
+        <v>1054.2</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -9761,13 +9761,13 @@
         <v>1</v>
       </c>
       <c r="U124" t="n">
-        <v>24.35644686299616</v>
+        <v>21.65325554923164</v>
       </c>
       <c r="V124" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="W124" t="n">
-        <v>-3.111741357234313</v>
+        <v>2.350005691519637</v>
       </c>
     </row>
     <row r="125">
@@ -9782,13 +9782,13 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D125" t="n">
-        <v>22.47</v>
+        <v>22.94</v>
       </c>
       <c r="E125" t="n">
-        <v>1348.2</v>
+        <v>1376.4</v>
       </c>
       <c r="F125" t="n">
         <v>0</v>
@@ -9836,13 +9836,13 @@
         <v>0</v>
       </c>
       <c r="U125" t="n">
-        <v>20.45494882064975</v>
+        <v>20.0358631211857</v>
       </c>
       <c r="V125" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W125" t="n">
-        <v>23.18228304405875</v>
+        <v>21.61755013077594</v>
       </c>
     </row>
     <row r="126">
@@ -9857,13 +9857,13 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D126" t="n">
-        <v>5.28</v>
+        <v>6.25</v>
       </c>
       <c r="E126" t="n">
-        <v>316.8</v>
+        <v>375</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -9911,13 +9911,13 @@
         <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>6.735340909090908</v>
+        <v>5.690016</v>
       </c>
       <c r="V126" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="W126" t="n">
-        <v>-148.49</v>
+        <v>-109.924352</v>
       </c>
     </row>
     <row r="127">
@@ -10007,37 +10007,37 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D128" t="n">
-        <v>33.54</v>
+        <v>38.52</v>
       </c>
       <c r="E128" t="n">
-        <v>2012.4</v>
+        <v>2311.2</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H128" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I128" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J128" t="n">
         <v>5</v>
       </c>
       <c r="K128" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L128" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M128" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="N128" t="n">
         <v>0</v>
@@ -10049,25 +10049,25 @@
         <v>3</v>
       </c>
       <c r="Q128" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R128" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S128" t="n">
         <v>3</v>
       </c>
       <c r="T128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U128" t="n">
-        <v>44.77856887298748</v>
+        <v>44.12845794392524</v>
       </c>
       <c r="V128" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="W128" t="n">
-        <v>-30.1316159809183</v>
+        <v>-26.47009865005192</v>
       </c>
     </row>
     <row r="129">
@@ -10157,67 +10157,67 @@
         </is>
       </c>
       <c r="C130" t="n">
+        <v>7</v>
+      </c>
+      <c r="D130" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1143.6</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
         <v>6</v>
       </c>
-      <c r="D130" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="E130" t="n">
-        <v>879.6</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
+        <v>4</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
         <v>5</v>
       </c>
-      <c r="H130" t="n">
-        <v>4</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N130" t="n">
-        <v>0</v>
-      </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" t="n">
-        <v>3</v>
-      </c>
       <c r="S130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U130" t="n">
-        <v>23.58350613915416</v>
+        <v>20.77556138509969</v>
       </c>
       <c r="V130" t="n">
         <v>-6</v>
       </c>
       <c r="W130" t="n">
-        <v>-37.95391541609823</v>
+        <v>-28.70054564533054</v>
       </c>
     </row>
     <row r="131">
@@ -10682,13 +10682,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D137" t="n">
-        <v>25.02</v>
+        <v>25.14</v>
       </c>
       <c r="E137" t="n">
-        <v>1501.2</v>
+        <v>1508.4</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -10736,13 +10736,13 @@
         <v>4</v>
       </c>
       <c r="U137" t="n">
-        <v>13.32278177458033</v>
+        <v>13.25918854415274</v>
       </c>
       <c r="V137" t="n">
         <v>14</v>
       </c>
       <c r="W137" t="n">
-        <v>-6.040111910471623</v>
+        <v>-6.011280827366747</v>
       </c>
     </row>
     <row r="138">
@@ -10832,13 +10832,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D139" t="n">
-        <v>53.41999999999999</v>
+        <v>53.54</v>
       </c>
       <c r="E139" t="n">
-        <v>3205.2</v>
+        <v>3212.4</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -10886,13 +10886,13 @@
         <v>5</v>
       </c>
       <c r="U139" t="n">
-        <v>35.0819805316361</v>
+        <v>35.00335076578259</v>
       </c>
       <c r="V139" t="n">
         <v>11</v>
       </c>
       <c r="W139" t="n">
-        <v>-0.429460876076377</v>
+        <v>-0.4284983190138225</v>
       </c>
     </row>
     <row r="140">
@@ -11057,13 +11057,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D142" t="n">
-        <v>16.56</v>
+        <v>16.68</v>
       </c>
       <c r="E142" t="n">
-        <v>993.6000000000001</v>
+        <v>1000.8</v>
       </c>
       <c r="F142" t="n">
         <v>0</v>
@@ -11096,7 +11096,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q142" t="n">
         <v>0</v>
@@ -11111,13 +11111,13 @@
         <v>2</v>
       </c>
       <c r="U142" t="n">
-        <v>13.26155797101449</v>
+        <v>13.88557553956834</v>
       </c>
       <c r="V142" t="n">
         <v>-1</v>
       </c>
       <c r="W142" t="n">
-        <v>-13.42030797101449</v>
+        <v>-13.32375899280575</v>
       </c>
     </row>
     <row r="143">
@@ -11207,13 +11207,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D144" t="n">
-        <v>28.46</v>
+        <v>28.58</v>
       </c>
       <c r="E144" t="n">
-        <v>1707.6</v>
+        <v>1714.8</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -11261,13 +11261,13 @@
         <v>0</v>
       </c>
       <c r="U144" t="n">
-        <v>7.025144061841181</v>
+        <v>6.995647305808258</v>
       </c>
       <c r="V144" t="n">
         <v>25</v>
       </c>
       <c r="W144" t="n">
-        <v>18.0370063246662</v>
+        <v>17.96127361791463</v>
       </c>
     </row>
     <row r="145">
@@ -11282,13 +11282,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="E145" t="n">
-        <v>213</v>
+        <v>220.2</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -11336,13 +11336,13 @@
         <v>0</v>
       </c>
       <c r="U145" t="n">
-        <v>9.780281690140844</v>
+        <v>9.460490463215258</v>
       </c>
       <c r="V145" t="n">
         <v>3</v>
       </c>
       <c r="W145" t="n">
-        <v>41.97323943661972</v>
+        <v>40.6008174386921</v>
       </c>
     </row>
     <row r="146">
@@ -12332,22 +12332,22 @@
         </is>
       </c>
       <c r="C159" t="n">
+        <v>8</v>
+      </c>
+      <c r="D159" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="E159" t="n">
+        <v>726.6</v>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="n">
         <v>7</v>
       </c>
-      <c r="D159" t="n">
-        <v>11.26</v>
-      </c>
-      <c r="E159" t="n">
-        <v>675.6</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0</v>
-      </c>
-      <c r="G159" t="n">
-        <v>6</v>
-      </c>
       <c r="H159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I159" t="n">
         <v>2</v>
@@ -12362,7 +12362,7 @@
         <v>4</v>
       </c>
       <c r="M159" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="N159" t="n">
         <v>0</v>
@@ -12374,7 +12374,7 @@
         <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -12386,13 +12386,13 @@
         <v>0</v>
       </c>
       <c r="U159" t="n">
-        <v>40.42587033747779</v>
+        <v>44.60737407101568</v>
       </c>
       <c r="V159" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W159" t="n">
-        <v>38.3294671403197</v>
+        <v>42.65811725846407</v>
       </c>
     </row>
     <row r="160">
@@ -12632,13 +12632,13 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D163" t="n">
-        <v>5.720000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="E163" t="n">
-        <v>343.2</v>
+        <v>375</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -12686,13 +12686,13 @@
         <v>0</v>
       </c>
       <c r="U163" t="n">
-        <v>10.83916083916084</v>
+        <v>9.92</v>
       </c>
       <c r="V163" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="W163" t="n">
-        <v>-10.8275</v>
+        <v>7.050672</v>
       </c>
     </row>
     <row r="164">
@@ -12707,13 +12707,13 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D164" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="E164" t="n">
-        <v>510</v>
+        <v>514.1999999999999</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -12767,7 +12767,7 @@
         <v>-3</v>
       </c>
       <c r="W164" t="n">
-        <v>28.81057647058823</v>
+        <v>28.57525087514586</v>
       </c>
     </row>
     <row r="165">
@@ -12782,13 +12782,13 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D165" t="n">
-        <v>16.33</v>
+        <v>17.18</v>
       </c>
       <c r="E165" t="n">
-        <v>979.8</v>
+        <v>1030.8</v>
       </c>
       <c r="F165" t="n">
         <v>0</v>
@@ -12836,13 +12836,13 @@
         <v>0</v>
       </c>
       <c r="U165" t="n">
-        <v>17.15181261481935</v>
+        <v>16.30320721769499</v>
       </c>
       <c r="V165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W165" t="n">
-        <v>41.4811818738518</v>
+        <v>44.37646682188591</v>
       </c>
     </row>
     <row r="166">
@@ -13007,13 +13007,13 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D168" t="n">
-        <v>6.39</v>
+        <v>7.24</v>
       </c>
       <c r="E168" t="n">
-        <v>383.4</v>
+        <v>434.4</v>
       </c>
       <c r="F168" t="n">
         <v>0</v>
@@ -13061,13 +13061,13 @@
         <v>1</v>
       </c>
       <c r="U168" t="n">
-        <v>40.2169014084507</v>
+        <v>35.49530386740332</v>
       </c>
       <c r="V168" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="W168" t="n">
-        <v>17.15186228482003</v>
+        <v>26.87850828729281</v>
       </c>
     </row>
     <row r="169">
@@ -13082,13 +13082,13 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="E169" t="n">
-        <v>109.2</v>
+        <v>124.2</v>
       </c>
       <c r="F169" t="n">
         <v>0</v>
@@ -13136,88 +13136,88 @@
         <v>1</v>
       </c>
       <c r="U169" t="n">
-        <v>51.28461538461538</v>
+        <v>45.09082125603864</v>
       </c>
       <c r="V169" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="W169" t="n">
-        <v>-138.7769230769231</v>
+        <v>-122.016425120773</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>MELILLA CIUDAD DEL DEPORTE</t>
+          <t>LEYMA CORUÑA</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>S. MICOVIC</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>21.85</v>
+        <v>0.85</v>
       </c>
       <c r="E170" t="n">
-        <v>1311</v>
+        <v>51</v>
       </c>
       <c r="F170" t="n">
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>0.2857142857142857</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
         <v>0</v>
       </c>
       <c r="O170" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P170" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
         <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U170" t="n">
-        <v>41.86290160183066</v>
+        <v>0</v>
       </c>
       <c r="V170" t="n">
-        <v>-23</v>
+        <v>-1</v>
       </c>
       <c r="W170" t="n">
-        <v>-57.86486041189931</v>
+        <v>100</v>
       </c>
     </row>
     <row r="171">
@@ -13228,71 +13228,71 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>D. POIRIER</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D171" t="n">
-        <v>7.08</v>
+        <v>25.25</v>
       </c>
       <c r="E171" t="n">
-        <v>424.8</v>
+        <v>1515</v>
       </c>
       <c r="F171" t="n">
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L171" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="N171" t="n">
         <v>0</v>
       </c>
       <c r="O171" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q171" t="n">
         <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S171" t="n">
         <v>2</v>
       </c>
       <c r="T171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U171" t="n">
-        <v>6.394576271186441</v>
+        <v>42.67851089108911</v>
       </c>
       <c r="V171" t="n">
-        <v>-8</v>
+        <v>-18</v>
       </c>
       <c r="W171" t="n">
-        <v>-45.08932203389831</v>
+        <v>-40.16131485148514</v>
       </c>
     </row>
     <row r="172">
@@ -13303,17 +13303,17 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>D. POIRIER</t>
         </is>
       </c>
       <c r="C172" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D172" t="n">
-        <v>8.289999999999999</v>
+        <v>7.08</v>
       </c>
       <c r="E172" t="n">
-        <v>497.4</v>
+        <v>424.8</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -13331,10 +13331,10 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M172" t="n">
         <v>0</v>
@@ -13343,31 +13343,31 @@
         <v>0</v>
       </c>
       <c r="O172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T172" t="n">
         <v>1</v>
       </c>
       <c r="U172" t="n">
-        <v>12.85886610373945</v>
+        <v>6.394576271186441</v>
       </c>
       <c r="V172" t="n">
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="W172" t="n">
-        <v>-51.28464414957781</v>
+        <v>-45.08932203389831</v>
       </c>
     </row>
     <row r="173">
@@ -13378,29 +13378,29 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>J. EZQUERRA TRELLES</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D173" t="n">
-        <v>0.63</v>
+        <v>10.41</v>
       </c>
       <c r="E173" t="n">
-        <v>37.8</v>
+        <v>624.6</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13418,31 +13418,31 @@
         <v>0</v>
       </c>
       <c r="O173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U173" t="n">
-        <v>0</v>
+        <v>17.02781940441883</v>
       </c>
       <c r="V173" t="n">
-        <v>-1</v>
+        <v>-20</v>
       </c>
       <c r="W173" t="n">
-        <v>0</v>
+        <v>-78.68281460134486</v>
       </c>
     </row>
     <row r="174">
@@ -13453,29 +13453,29 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>J. EZQUERRA TRELLES</t>
         </is>
       </c>
       <c r="C174" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>9.640000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="E174" t="n">
-        <v>578.4</v>
+        <v>37.8</v>
       </c>
       <c r="F174" t="n">
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -13511,13 +13511,13 @@
         <v>0</v>
       </c>
       <c r="U174" t="n">
-        <v>25.97572614107884</v>
+        <v>0</v>
       </c>
       <c r="V174" t="n">
-        <v>-10</v>
+        <v>-1</v>
       </c>
       <c r="W174" t="n">
-        <v>-47.52873443983403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -13528,32 +13528,32 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>J. GODSPOWER JOHNSON</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D175" t="n">
-        <v>11.66</v>
+        <v>12.32</v>
       </c>
       <c r="E175" t="n">
-        <v>699.6</v>
+        <v>739.2</v>
       </c>
       <c r="F175" t="n">
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" t="n">
         <v>2</v>
       </c>
       <c r="J175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -13562,37 +13562,37 @@
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
         <v>0</v>
       </c>
       <c r="O175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
         <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T175" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U175" t="n">
-        <v>17.00831903945112</v>
+        <v>20.32516233766233</v>
       </c>
       <c r="V175" t="n">
-        <v>-14</v>
+        <v>-5</v>
       </c>
       <c r="W175" t="n">
-        <v>-42.61677530017152</v>
+        <v>-27.28326298701299</v>
       </c>
     </row>
     <row r="176">
@@ -13603,26 +13603,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>M. CAICEDO SANCHEZ</t>
+          <t>J. GODSPOWER JOHNSON</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D176" t="n">
-        <v>11.42</v>
+        <v>15.04</v>
       </c>
       <c r="E176" t="n">
-        <v>685.2</v>
+        <v>902.4</v>
       </c>
       <c r="F176" t="n">
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I176" t="n">
         <v>2</v>
@@ -13631,43 +13631,43 @@
         <v>1</v>
       </c>
       <c r="K176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="N176" t="n">
         <v>0</v>
       </c>
       <c r="O176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T176" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U176" t="n">
-        <v>35.44805604203152</v>
+        <v>13.18597074468085</v>
       </c>
       <c r="V176" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="W176" t="n">
-        <v>-11.98265323992996</v>
+        <v>-17.98889627659575</v>
       </c>
     </row>
     <row r="177">
@@ -13678,47 +13678,47 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>M. CAICEDO SANCHEZ</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D177" t="n">
-        <v>7.68</v>
+        <v>14.44</v>
       </c>
       <c r="E177" t="n">
-        <v>460.8</v>
+        <v>866.4</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177" t="n">
         <v>2</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N177" t="n">
         <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P177" t="n">
         <v>3</v>
@@ -13736,13 +13736,13 @@
         <v>1</v>
       </c>
       <c r="U177" t="n">
-        <v>30.40346354166667</v>
+        <v>31.82404432132964</v>
       </c>
       <c r="V177" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="W177" t="n">
-        <v>-28.0787109375</v>
+        <v>-7.389355955678677</v>
       </c>
     </row>
     <row r="178">
@@ -13753,26 +13753,26 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="C178" t="n">
         <v>4</v>
       </c>
       <c r="D178" t="n">
-        <v>6.42</v>
+        <v>7.68</v>
       </c>
       <c r="E178" t="n">
-        <v>385.2</v>
+        <v>460.8</v>
       </c>
       <c r="F178" t="n">
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I178" t="n">
         <v>0</v>
@@ -13781,43 +13781,43 @@
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L178" t="n">
         <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N178" t="n">
         <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q178" t="n">
         <v>1</v>
       </c>
       <c r="R178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S178" t="n">
         <v>0</v>
       </c>
       <c r="T178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U178" t="n">
-        <v>9.326869158878507</v>
+        <v>30.40346354166667</v>
       </c>
       <c r="V178" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="W178" t="n">
-        <v>-18.00699376947041</v>
+        <v>-28.0787109375</v>
       </c>
     </row>
     <row r="179">
@@ -13828,32 +13828,32 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>N. HOOVER</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="C179" t="n">
         <v>5</v>
       </c>
       <c r="D179" t="n">
-        <v>11.1</v>
+        <v>6.600000000000001</v>
       </c>
       <c r="E179" t="n">
-        <v>666</v>
+        <v>396</v>
       </c>
       <c r="F179" t="n">
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H179" t="n">
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -13862,37 +13862,37 @@
         <v>0</v>
       </c>
       <c r="M179" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="N179" t="n">
         <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P179" t="n">
         <v>1</v>
       </c>
       <c r="Q179" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R179" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S179" t="n">
         <v>0</v>
       </c>
       <c r="T179" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U179" t="n">
-        <v>48.89036036036037</v>
+        <v>11.79977272727273</v>
       </c>
       <c r="V179" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="W179" t="n">
-        <v>-22.7547027027027</v>
+        <v>-17.51589393939394</v>
       </c>
     </row>
     <row r="180">
@@ -13903,17 +13903,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>N. MC MULLEN</t>
+          <t>N. HOOVER</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D180" t="n">
-        <v>2.62</v>
+        <v>12.03</v>
       </c>
       <c r="E180" t="n">
-        <v>157.2</v>
+        <v>721.8</v>
       </c>
       <c r="F180" t="n">
         <v>0</v>
@@ -13922,22 +13922,22 @@
         <v>5</v>
       </c>
       <c r="H180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M180" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N180" t="n">
         <v>0</v>
@@ -13946,28 +13946,28 @@
         <v>0</v>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q180" t="n">
         <v>0</v>
       </c>
       <c r="R180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T180" t="n">
         <v>0</v>
       </c>
       <c r="U180" t="n">
-        <v>62.13427480916031</v>
+        <v>47.47330008312553</v>
       </c>
       <c r="V180" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="W180" t="n">
-        <v>-1.697519083969466</v>
+        <v>-12.94256857855361</v>
       </c>
     </row>
     <row r="181">
@@ -13978,41 +13978,41 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>P. CORDOBA MURO</t>
+          <t>N. MC MULLEN</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>19.89</v>
+        <v>2.95</v>
       </c>
       <c r="E181" t="n">
-        <v>1193.4</v>
+        <v>177</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="N181" t="n">
         <v>0</v>
@@ -14027,22 +14027,22 @@
         <v>0</v>
       </c>
       <c r="R181" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U181" t="n">
-        <v>24.12083961789844</v>
+        <v>55.18366101694915</v>
       </c>
       <c r="V181" t="n">
-        <v>-23</v>
+        <v>4</v>
       </c>
       <c r="W181" t="n">
-        <v>-48.43214680744093</v>
+        <v>11.20464406779661</v>
       </c>
     </row>
     <row r="182">
@@ -14053,41 +14053,41 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>P. KRUTOUS</t>
+          <t>P. CORDOBA MURO</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D182" t="n">
-        <v>2.05</v>
+        <v>20.12</v>
       </c>
       <c r="E182" t="n">
-        <v>123</v>
+        <v>1207.2</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N182" t="n">
         <v>0</v>
@@ -14102,22 +14102,22 @@
         <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S182" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U182" t="n">
-        <v>34.14634146341464</v>
+        <v>23.84510437375745</v>
       </c>
       <c r="V182" t="n">
-        <v>-5</v>
+        <v>-21</v>
       </c>
       <c r="W182" t="n">
-        <v>-62.65531707317073</v>
+        <v>-47.87849900596422</v>
       </c>
     </row>
     <row r="183">
@@ -14128,23 +14128,23 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>P. KRUTOUS</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D183" t="n">
-        <v>5.87</v>
+        <v>2.05</v>
       </c>
       <c r="E183" t="n">
-        <v>352.2</v>
+        <v>123</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -14180,19 +14180,19 @@
         <v>1</v>
       </c>
       <c r="S183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U183" t="n">
-        <v>0</v>
+        <v>34.14634146341464</v>
       </c>
       <c r="V183" t="n">
-        <v>-13</v>
+        <v>-5</v>
       </c>
       <c r="W183" t="n">
-        <v>-58.03255536626917</v>
+        <v>-62.65531707317073</v>
       </c>
     </row>
     <row r="184">
@@ -14203,41 +14203,41 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>S. CECCARDI</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D184" t="n">
-        <v>4.15</v>
+        <v>5.87</v>
       </c>
       <c r="E184" t="n">
-        <v>249</v>
+        <v>352.2</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N184" t="n">
         <v>0</v>
@@ -14255,19 +14255,19 @@
         <v>1</v>
       </c>
       <c r="S184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U184" t="n">
-        <v>25.08334939759036</v>
+        <v>0</v>
       </c>
       <c r="V184" t="n">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="W184" t="n">
-        <v>-32.86771084337349</v>
+        <v>-58.03255536626917</v>
       </c>
     </row>
     <row r="185">
@@ -14278,41 +14278,41 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ FEBLES</t>
+          <t>S. CECCARDI</t>
         </is>
       </c>
       <c r="C185" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D185" t="n">
-        <v>16.28</v>
+        <v>7.75</v>
       </c>
       <c r="E185" t="n">
-        <v>976.8</v>
+        <v>465</v>
       </c>
       <c r="F185" t="n">
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H185" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I185" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M185" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="N185" t="n">
         <v>0</v>
@@ -14321,103 +14321,103 @@
         <v>0</v>
       </c>
       <c r="P185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
         <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U185" t="n">
-        <v>17.85925061425061</v>
+        <v>29.90347096774194</v>
       </c>
       <c r="V185" t="n">
-        <v>-12</v>
+        <v>-3</v>
       </c>
       <c r="W185" t="n">
-        <v>-48.60700245700246</v>
+        <v>3.995225806451614</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>MONBUS OBRADOIRO</t>
+          <t>MELILLA CIUDAD DEL DEPORTE</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>S. RODRIGUEZ FEBLES</t>
         </is>
       </c>
       <c r="C186" t="n">
         <v>8</v>
       </c>
       <c r="D186" t="n">
-        <v>26.08</v>
+        <v>19.63</v>
       </c>
       <c r="E186" t="n">
-        <v>1564.8</v>
+        <v>1177.8</v>
       </c>
       <c r="F186" t="n">
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H186" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I186" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K186" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.625</v>
       </c>
       <c r="N186" t="n">
         <v>0</v>
       </c>
       <c r="O186" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U186" t="n">
-        <v>37.37753450920246</v>
+        <v>17.83719307182883</v>
       </c>
       <c r="V186" t="n">
-        <v>9</v>
+        <v>-5</v>
       </c>
       <c r="W186" t="n">
-        <v>2.350920245398774</v>
+        <v>-18.22371370351502</v>
       </c>
     </row>
     <row r="187">
@@ -14428,71 +14428,71 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D187" t="n">
-        <v>13.04</v>
+        <v>26.08</v>
       </c>
       <c r="E187" t="n">
-        <v>782.4000000000001</v>
+        <v>1564.8</v>
       </c>
       <c r="F187" t="n">
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H187" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J187" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K187" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L187" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M187" t="n">
-        <v>1</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="N187" t="n">
         <v>0</v>
       </c>
       <c r="O187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P187" t="n">
         <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T187" t="n">
         <v>0</v>
       </c>
       <c r="U187" t="n">
-        <v>10.65963190184049</v>
+        <v>37.37753450920246</v>
       </c>
       <c r="V187" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="W187" t="n">
-        <v>24.51968558282208</v>
+        <v>2.350920245398774</v>
       </c>
     </row>
     <row r="188">
@@ -14503,71 +14503,71 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="C188" t="n">
         <v>7</v>
       </c>
       <c r="D188" t="n">
-        <v>14.14</v>
+        <v>13.04</v>
       </c>
       <c r="E188" t="n">
-        <v>848.4</v>
+        <v>782.4000000000001</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H188" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I188" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M188" t="n">
-        <v>0.6875</v>
+        <v>1</v>
       </c>
       <c r="N188" t="n">
         <v>0</v>
       </c>
       <c r="O188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
       </c>
       <c r="T188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U188" t="n">
-        <v>25.49298444130127</v>
+        <v>10.65963190184049</v>
       </c>
       <c r="V188" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="W188" t="n">
-        <v>28.22802687411598</v>
+        <v>24.51968558282208</v>
       </c>
     </row>
     <row r="189">
@@ -14578,41 +14578,41 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D189" t="n">
-        <v>8.34</v>
+        <v>14.14</v>
       </c>
       <c r="E189" t="n">
-        <v>500.4</v>
+        <v>848.4</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K189" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>0.6875</v>
       </c>
       <c r="N189" t="n">
         <v>0</v>
@@ -14621,28 +14621,28 @@
         <v>0</v>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q189" t="n">
         <v>1</v>
       </c>
       <c r="R189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T189" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U189" t="n">
-        <v>12.50384892086331</v>
+        <v>25.49298444130127</v>
       </c>
       <c r="V189" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="W189" t="n">
-        <v>-38.1000839328537</v>
+        <v>28.22802687411598</v>
       </c>
     </row>
     <row r="190">
@@ -14653,26 +14653,26 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="C190" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D190" t="n">
-        <v>23.83</v>
+        <v>8.34</v>
       </c>
       <c r="E190" t="n">
-        <v>1429.8</v>
+        <v>500.4</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H190" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -14681,13 +14681,13 @@
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L190" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
         <v>0</v>
@@ -14696,28 +14696,28 @@
         <v>0</v>
       </c>
       <c r="P190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q190" t="n">
         <v>1</v>
       </c>
       <c r="R190" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U190" t="n">
-        <v>20.89023499790181</v>
+        <v>12.50384892086331</v>
       </c>
       <c r="V190" t="n">
-        <v>24</v>
+        <v>-3</v>
       </c>
       <c r="W190" t="n">
-        <v>28.12888375996643</v>
+        <v>-38.1000839328537</v>
       </c>
     </row>
     <row r="191">
@@ -14728,41 +14728,41 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>K. LUNDQVIST</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D191" t="n">
-        <v>3.68</v>
+        <v>23.83</v>
       </c>
       <c r="E191" t="n">
-        <v>220.8</v>
+        <v>1429.8</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H191" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M191" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="N191" t="n">
         <v>0</v>
@@ -14771,28 +14771,28 @@
         <v>0</v>
       </c>
       <c r="P191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U191" t="n">
-        <v>47.47</v>
+        <v>20.89023499790181</v>
       </c>
       <c r="V191" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="W191" t="n">
-        <v>44.09</v>
+        <v>28.12888375996643</v>
       </c>
     </row>
     <row r="192">
@@ -14803,71 +14803,71 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>K. LUNDQVIST</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>21.36</v>
+        <v>3.68</v>
       </c>
       <c r="E192" t="n">
-        <v>1281.6</v>
+        <v>220.8</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H192" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N192" t="n">
         <v>0</v>
       </c>
       <c r="O192" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R192" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U192" t="n">
-        <v>36.13929307116105</v>
+        <v>47.47</v>
       </c>
       <c r="V192" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="W192" t="n">
-        <v>-13.37974250936329</v>
+        <v>44.09</v>
       </c>
     </row>
     <row r="193">
@@ -14878,41 +14878,41 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>M. SPEIGHT</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="C193" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D193" t="n">
-        <v>5.22</v>
+        <v>21.36</v>
       </c>
       <c r="E193" t="n">
-        <v>313.2</v>
+        <v>1281.6</v>
       </c>
       <c r="F193" t="n">
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H193" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I193" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K193" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L193" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M193" t="n">
-        <v>0.5</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="N193" t="n">
         <v>0</v>
@@ -14921,28 +14921,28 @@
         <v>4</v>
       </c>
       <c r="P193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R193" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S193" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T193" t="n">
         <v>1</v>
       </c>
       <c r="U193" t="n">
-        <v>43.96141762452108</v>
+        <v>36.13929307116105</v>
       </c>
       <c r="V193" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="W193" t="n">
-        <v>13.36779693486591</v>
+        <v>-13.37974250936329</v>
       </c>
     </row>
     <row r="194">
@@ -14953,71 +14953,71 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>M. SPEIGHT</t>
         </is>
       </c>
       <c r="C194" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D194" t="n">
-        <v>15.61</v>
+        <v>5.22</v>
       </c>
       <c r="E194" t="n">
-        <v>936.6</v>
+        <v>313.2</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I194" t="n">
         <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K194" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N194" t="n">
         <v>0</v>
       </c>
       <c r="O194" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P194" t="n">
         <v>1</v>
       </c>
       <c r="Q194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S194" t="n">
         <v>1</v>
       </c>
       <c r="T194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U194" t="n">
-        <v>12.36339525944907</v>
+        <v>43.96141762452108</v>
       </c>
       <c r="V194" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W194" t="n">
-        <v>17.92648302370275</v>
+        <v>13.36779693486591</v>
       </c>
     </row>
     <row r="195">
@@ -15028,38 +15028,38 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="C195" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D195" t="n">
-        <v>6.51</v>
+        <v>15.61</v>
       </c>
       <c r="E195" t="n">
-        <v>390.6</v>
+        <v>936.6</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -15071,28 +15071,28 @@
         <v>1</v>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U195" t="n">
-        <v>0</v>
+        <v>12.36339525944907</v>
       </c>
       <c r="V195" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="W195" t="n">
-        <v>56.96227342549923</v>
+        <v>17.92648302370275</v>
       </c>
     </row>
     <row r="196">
@@ -15103,47 +15103,47 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="C196" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D196" t="n">
-        <v>3.98</v>
+        <v>6.51</v>
       </c>
       <c r="E196" t="n">
-        <v>238.8</v>
+        <v>390.6</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
         <v>0</v>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P196" t="n">
         <v>0</v>
@@ -15152,22 +15152,22 @@
         <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
       </c>
       <c r="T196" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U196" t="n">
-        <v>17.0427135678392</v>
+        <v>0</v>
       </c>
       <c r="V196" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="W196" t="n">
-        <v>1.534321608040196</v>
+        <v>56.96227342549923</v>
       </c>
     </row>
     <row r="197">
@@ -15178,23 +15178,23 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D197" t="n">
-        <v>20.85</v>
+        <v>3.98</v>
       </c>
       <c r="E197" t="n">
-        <v>1251</v>
+        <v>238.8</v>
       </c>
       <c r="F197" t="n">
         <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H197" t="n">
         <v>1</v>
@@ -15203,121 +15203,121 @@
         <v>1</v>
       </c>
       <c r="J197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="N197" t="n">
         <v>0</v>
       </c>
       <c r="O197" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
         <v>2</v>
       </c>
       <c r="S197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U197" t="n">
-        <v>10.67719424460432</v>
+        <v>17.0427135678392</v>
       </c>
       <c r="V197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="W197" t="n">
-        <v>0.09753956834532441</v>
+        <v>1.534321608040196</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>MOVISTAR ESTUDIANTES</t>
+          <t>MONBUS OBRADOIRO</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D198" t="n">
-        <v>3.61</v>
+        <v>20.85</v>
       </c>
       <c r="E198" t="n">
-        <v>216.6</v>
+        <v>1251</v>
       </c>
       <c r="F198" t="n">
         <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N198" t="n">
         <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P198" t="n">
         <v>1</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U198" t="n">
-        <v>26.0387811634349</v>
+        <v>10.67719424460432</v>
       </c>
       <c r="V198" t="n">
-        <v>-5</v>
+        <v>10</v>
       </c>
       <c r="W198" t="n">
-        <v>-69.09457063711912</v>
+        <v>0.09753956834532441</v>
       </c>
     </row>
     <row r="199">
@@ -15328,17 +15328,17 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>A. GONZÁLEZ PÉREZ</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D199" t="n">
-        <v>2.4</v>
+        <v>3.61</v>
       </c>
       <c r="E199" t="n">
-        <v>144</v>
+        <v>216.6</v>
       </c>
       <c r="F199" t="n">
         <v>0</v>
@@ -15368,10 +15368,10 @@
         <v>0</v>
       </c>
       <c r="O199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q199" t="n">
         <v>0</v>
@@ -15386,13 +15386,13 @@
         <v>0</v>
       </c>
       <c r="U199" t="n">
-        <v>0</v>
+        <v>26.0387811634349</v>
       </c>
       <c r="V199" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="W199" t="n">
-        <v>-5.870416666666665</v>
+        <v>-69.09457063711912</v>
       </c>
     </row>
     <row r="200">
@@ -15403,29 +15403,29 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>G. FILIPOVIC</t>
+          <t>A. GONZÁLEZ PÉREZ</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D200" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="E200" t="n">
-        <v>100.8</v>
+        <v>144</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -15437,13 +15437,13 @@
         <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
         <v>0</v>
       </c>
       <c r="O200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P200" t="n">
         <v>0</v>
@@ -15461,13 +15461,13 @@
         <v>0</v>
       </c>
       <c r="U200" t="n">
-        <v>61.90476190476191</v>
+        <v>0</v>
       </c>
       <c r="V200" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W200" t="n">
-        <v>35.66476190476191</v>
+        <v>-5.870416666666665</v>
       </c>
     </row>
     <row r="201">
@@ -15478,71 +15478,71 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>J. GRANGER</t>
+          <t>G. FILIPOVIC</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D201" t="n">
-        <v>25.69</v>
+        <v>1.68</v>
       </c>
       <c r="E201" t="n">
-        <v>1541.4</v>
+        <v>100.8</v>
       </c>
       <c r="F201" t="n">
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H201" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I201" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L201" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="N201" t="n">
         <v>0</v>
       </c>
       <c r="O201" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S201" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T201" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U201" t="n">
-        <v>48.95202413390425</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="V201" t="n">
-        <v>-17</v>
+        <v>3</v>
       </c>
       <c r="W201" t="n">
-        <v>-59.42093032308291</v>
+        <v>35.66476190476191</v>
       </c>
     </row>
     <row r="202">
@@ -15553,35 +15553,35 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>J. VAULET</t>
+          <t>H. LOPEZ BARRANTES</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>9.08</v>
+        <v>1.98</v>
       </c>
       <c r="E202" t="n">
-        <v>544.8</v>
+        <v>118.8</v>
       </c>
       <c r="F202" t="n">
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L202" t="n">
         <v>0</v>
@@ -15596,28 +15596,28 @@
         <v>0</v>
       </c>
       <c r="P202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U202" t="n">
-        <v>12.70254405286344</v>
+        <v>22.68</v>
       </c>
       <c r="V202" t="n">
-        <v>-11</v>
+        <v>-1</v>
       </c>
       <c r="W202" t="n">
-        <v>-93.92861233480177</v>
+        <v>-40.97999999999999</v>
       </c>
     </row>
     <row r="203">
@@ -15628,71 +15628,71 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>L. GIOVANNETTI</t>
+          <t>J. GRANGER</t>
         </is>
       </c>
       <c r="C203" t="n">
+        <v>11</v>
+      </c>
+      <c r="D203" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1804.2</v>
+      </c>
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="n">
+        <v>22</v>
+      </c>
+      <c r="H203" t="n">
+        <v>3</v>
+      </c>
+      <c r="I203" t="n">
+        <v>9</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>6</v>
+      </c>
+      <c r="L203" t="n">
+        <v>6</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>4</v>
+      </c>
+      <c r="P203" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>1</v>
+      </c>
+      <c r="R203" t="n">
+        <v>9</v>
+      </c>
+      <c r="S203" t="n">
+        <v>4</v>
+      </c>
+      <c r="T203" t="n">
         <v>5</v>
       </c>
-      <c r="D203" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="E203" t="n">
-        <v>374.4</v>
-      </c>
-      <c r="F203" t="n">
-        <v>0</v>
-      </c>
-      <c r="G203" t="n">
-        <v>1</v>
-      </c>
-      <c r="H203" t="n">
-        <v>1</v>
-      </c>
-      <c r="I203" t="n">
-        <v>1</v>
-      </c>
-      <c r="J203" t="n">
-        <v>1</v>
-      </c>
-      <c r="K203" t="n">
-        <v>0</v>
-      </c>
-      <c r="L203" t="n">
-        <v>0</v>
-      </c>
-      <c r="M203" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N203" t="n">
-        <v>0</v>
-      </c>
-      <c r="O203" t="n">
-        <v>0</v>
-      </c>
-      <c r="P203" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
-      <c r="R203" t="n">
-        <v>0</v>
-      </c>
-      <c r="S203" t="n">
-        <v>0</v>
-      </c>
-      <c r="T203" t="n">
-        <v>0</v>
-      </c>
       <c r="U203" t="n">
-        <v>8.418830128205126</v>
+        <v>47.36694712337879</v>
       </c>
       <c r="V203" t="n">
-        <v>3</v>
+        <v>-14</v>
       </c>
       <c r="W203" t="n">
-        <v>-24.74078525641026</v>
+        <v>-44.92761223811107</v>
       </c>
     </row>
     <row r="204">
@@ -15703,71 +15703,71 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>L. NWOGBO</t>
+          <t>J. VAULET</t>
         </is>
       </c>
       <c r="C204" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D204" t="n">
-        <v>17.21</v>
+        <v>9.08</v>
       </c>
       <c r="E204" t="n">
-        <v>1032.6</v>
+        <v>544.8</v>
       </c>
       <c r="F204" t="n">
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H204" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
         <v>0</v>
       </c>
       <c r="O204" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q204" t="n">
         <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S204" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T204" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U204" t="n">
-        <v>31.5577106333527</v>
+        <v>12.70254405286344</v>
       </c>
       <c r="V204" t="n">
-        <v>-7</v>
+        <v>-11</v>
       </c>
       <c r="W204" t="n">
-        <v>-24.56108076699594</v>
+        <v>-93.92861233480177</v>
       </c>
     </row>
     <row r="205">
@@ -15778,53 +15778,53 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>O. SILVERIO GRULLON</t>
+          <t>L. GIOVANNETTI</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D205" t="n">
-        <v>12.37</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E205" t="n">
-        <v>742.2</v>
+        <v>493.2</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
         <v>1</v>
       </c>
       <c r="K205" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>0.5833333333333334</v>
+        <v>1.5</v>
       </c>
       <c r="N205" t="n">
         <v>0</v>
       </c>
       <c r="O205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R205" t="n">
         <v>0</v>
@@ -15836,13 +15836,13 @@
         <v>0</v>
       </c>
       <c r="U205" t="n">
-        <v>31.6070735650768</v>
+        <v>6.390936739659367</v>
       </c>
       <c r="V205" t="n">
-        <v>-19</v>
+        <v>2</v>
       </c>
       <c r="W205" t="n">
-        <v>-50.83189975747777</v>
+        <v>-28.65242092457421</v>
       </c>
     </row>
     <row r="206">
@@ -15853,71 +15853,71 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>P. GARINO GULLOTTA</t>
+          <t>L. NWOGBO</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D206" t="n">
-        <v>31.25</v>
+        <v>19.61</v>
       </c>
       <c r="E206" t="n">
-        <v>1875</v>
+        <v>1176.6</v>
       </c>
       <c r="F206" t="n">
         <v>0</v>
       </c>
       <c r="G206" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H206" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I206" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K206" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M206" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="N206" t="n">
         <v>0</v>
       </c>
       <c r="O206" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q206" t="n">
         <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="S206" t="n">
         <v>3</v>
       </c>
       <c r="T206" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U206" t="n">
-        <v>22.8151616</v>
+        <v>33.81479857215707</v>
       </c>
       <c r="V206" t="n">
-        <v>-23</v>
+        <v>-3</v>
       </c>
       <c r="W206" t="n">
-        <v>-54.4114528</v>
+        <v>-7.359520652728206</v>
       </c>
     </row>
     <row r="207">
@@ -15928,53 +15928,53 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>R. STUMBRIS</t>
+          <t>O. SILVERIO GRULLON</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D207" t="n">
-        <v>1.36</v>
+        <v>12.37</v>
       </c>
       <c r="E207" t="n">
-        <v>81.59999999999999</v>
+        <v>742.2</v>
       </c>
       <c r="F207" t="n">
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H207" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K207" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M207" t="n">
-        <v>1</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="N207" t="n">
         <v>0</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R207" t="n">
         <v>0</v>
@@ -15986,13 +15986,13 @@
         <v>0</v>
       </c>
       <c r="U207" t="n">
-        <v>15.92977941176471</v>
+        <v>31.6070735650768</v>
       </c>
       <c r="V207" t="n">
-        <v>-2</v>
+        <v>-19</v>
       </c>
       <c r="W207" t="n">
-        <v>-12.10235294117647</v>
+        <v>-50.83189975747777</v>
       </c>
     </row>
     <row r="208">
@@ -16003,71 +16003,71 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>S. GARCIA CALVO</t>
+          <t>P. GARINO GULLOTTA</t>
         </is>
       </c>
       <c r="C208" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D208" t="n">
-        <v>7</v>
+        <v>35.63</v>
       </c>
       <c r="E208" t="n">
-        <v>420</v>
+        <v>2137.8</v>
       </c>
       <c r="F208" t="n">
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H208" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="N208" t="n">
         <v>0</v>
       </c>
       <c r="O208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P208" t="n">
         <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S208" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T208" t="n">
         <v>1</v>
       </c>
       <c r="U208" t="n">
-        <v>17.055</v>
+        <v>21.57047431939376</v>
       </c>
       <c r="V208" t="n">
-        <v>-4</v>
+        <v>-20</v>
       </c>
       <c r="W208" t="n">
-        <v>13.03907142857143</v>
+        <v>-42.79560763401627</v>
       </c>
     </row>
     <row r="209">
@@ -16078,71 +16078,71 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>S. SALIN</t>
+          <t>R. STUMBRIS</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D209" t="n">
-        <v>17.44</v>
+        <v>1.36</v>
       </c>
       <c r="E209" t="n">
-        <v>1046.4</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F209" t="n">
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N209" t="n">
         <v>0</v>
       </c>
       <c r="O209" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q209" t="n">
         <v>0</v>
       </c>
       <c r="R209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S209" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T209" t="n">
         <v>0</v>
       </c>
       <c r="U209" t="n">
-        <v>16.43624426605504</v>
+        <v>15.92977941176471</v>
       </c>
       <c r="V209" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="W209" t="n">
-        <v>-48.74918004587155</v>
+        <v>-12.10235294117647</v>
       </c>
     </row>
     <row r="210">
@@ -16153,26 +16153,26 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>T. MC GREW</t>
+          <t>S. GARCIA CALVO</t>
         </is>
       </c>
       <c r="C210" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D210" t="n">
-        <v>27.9</v>
+        <v>7</v>
       </c>
       <c r="E210" t="n">
-        <v>1674</v>
+        <v>420</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H210" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I210" t="n">
         <v>1</v>
@@ -16181,82 +16181,82 @@
         <v>0</v>
       </c>
       <c r="K210" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L210" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M210" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N210" t="n">
         <v>0</v>
       </c>
       <c r="O210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P210" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R210" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S210" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T210" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="U210" t="n">
-        <v>19.523229390681</v>
+        <v>17.055</v>
       </c>
       <c r="V210" t="n">
-        <v>-15</v>
+        <v>-4</v>
       </c>
       <c r="W210" t="n">
-        <v>-38.30463799283154</v>
+        <v>13.03907142857143</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
+          <t>MOVISTAR ESTUDIANTES</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>A. CHAPELA LAGE</t>
+          <t>S. SALIN</t>
         </is>
       </c>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D211" t="n">
-        <v>2.53</v>
+        <v>19.84</v>
       </c>
       <c r="E211" t="n">
-        <v>151.8</v>
+        <v>1190.4</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -16268,7 +16268,7 @@
         <v>0</v>
       </c>
       <c r="O211" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P211" t="n">
         <v>1</v>
@@ -16277,67 +16277,67 @@
         <v>0</v>
       </c>
       <c r="R211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T211" t="n">
         <v>0</v>
       </c>
       <c r="U211" t="n">
-        <v>26.6</v>
+        <v>14.44798891129032</v>
       </c>
       <c r="V211" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="W211" t="n">
-        <v>-28.78</v>
+        <v>-28.25976310483871</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>PALMER BASKET MALLORCA PALMA</t>
+          <t>MOVISTAR ESTUDIANTES</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>T. MC GREW</t>
         </is>
       </c>
       <c r="C212" t="n">
+        <v>13</v>
+      </c>
+      <c r="D212" t="n">
+        <v>32.28</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1936.8</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>7</v>
+      </c>
+      <c r="H212" t="n">
         <v>5</v>
       </c>
-      <c r="D212" t="n">
-        <v>6.149999999999999</v>
-      </c>
-      <c r="E212" t="n">
-        <v>369</v>
-      </c>
-      <c r="F212" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0</v>
-      </c>
-      <c r="H212" t="n">
-        <v>0</v>
-      </c>
       <c r="I212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L212" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="N212" t="n">
         <v>0</v>
@@ -16346,28 +16346,28 @@
         <v>2</v>
       </c>
       <c r="P212" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q212" t="n">
         <v>0</v>
       </c>
       <c r="R212" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="S212" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T212" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U212" t="n">
-        <v>11.28367479674797</v>
+        <v>20.31792131350682</v>
       </c>
       <c r="V212" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="W212" t="n">
-        <v>-107.5185853658536</v>
+        <v>-27.66880421313507</v>
       </c>
     </row>
     <row r="213">
@@ -16378,26 +16378,26 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>A. CHAPELA LAGE</t>
         </is>
       </c>
       <c r="C213" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>26.33</v>
+        <v>2.53</v>
       </c>
       <c r="E213" t="n">
-        <v>1579.8</v>
+        <v>151.8</v>
       </c>
       <c r="F213" t="n">
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I213" t="n">
         <v>0</v>
@@ -16406,43 +16406,43 @@
         <v>0</v>
       </c>
       <c r="K213" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L213" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
         <v>0</v>
       </c>
       <c r="O213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q213" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T213" t="n">
         <v>0</v>
       </c>
       <c r="U213" t="n">
-        <v>12.85420053171288</v>
+        <v>26.6</v>
       </c>
       <c r="V213" t="n">
-        <v>-19</v>
+        <v>-2</v>
       </c>
       <c r="W213" t="n">
-        <v>-61.6627421192556</v>
+        <v>-28.78</v>
       </c>
     </row>
     <row r="214">
@@ -16453,38 +16453,38 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="C214" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D214" t="n">
-        <v>5.1</v>
+        <v>6.149999999999999</v>
       </c>
       <c r="E214" t="n">
-        <v>306</v>
+        <v>369</v>
       </c>
       <c r="F214" t="n">
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M214" t="n">
         <v>0</v>
@@ -16493,31 +16493,31 @@
         <v>0</v>
       </c>
       <c r="O214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q214" t="n">
         <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T214" t="n">
         <v>0</v>
       </c>
       <c r="U214" t="n">
-        <v>11.30605882352941</v>
+        <v>11.28367479674797</v>
       </c>
       <c r="V214" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="W214" t="n">
-        <v>23.56266666666667</v>
+        <v>-107.5185853658536</v>
       </c>
     </row>
     <row r="215">
@@ -16528,41 +16528,41 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>D. SANADZE</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="C215" t="n">
         <v>9</v>
       </c>
       <c r="D215" t="n">
-        <v>26.05</v>
+        <v>26.33</v>
       </c>
       <c r="E215" t="n">
-        <v>1563</v>
+        <v>1579.8</v>
       </c>
       <c r="F215" t="n">
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H215" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I215" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J215" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L215" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M215" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="N215" t="n">
         <v>0</v>
@@ -16574,25 +16574,25 @@
         <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R215" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S215" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U215" t="n">
-        <v>49.98703646833013</v>
+        <v>12.85420053171288</v>
       </c>
       <c r="V215" t="n">
         <v>-19</v>
       </c>
       <c r="W215" t="n">
-        <v>-40.98514011516315</v>
+        <v>-61.6627421192556</v>
       </c>
     </row>
     <row r="216">
@@ -16603,71 +16603,71 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="C216" t="n">
+        <v>4</v>
+      </c>
+      <c r="D216" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E216" t="n">
+        <v>306</v>
+      </c>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="n">
+        <v>1</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>0</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>0</v>
+      </c>
+      <c r="R216" t="n">
+        <v>0</v>
+      </c>
+      <c r="S216" t="n">
+        <v>0</v>
+      </c>
+      <c r="T216" t="n">
+        <v>0</v>
+      </c>
+      <c r="U216" t="n">
+        <v>11.30605882352941</v>
+      </c>
+      <c r="V216" t="n">
         <v>5</v>
       </c>
-      <c r="D216" t="n">
-        <v>12.52</v>
-      </c>
-      <c r="E216" t="n">
-        <v>751.2</v>
-      </c>
-      <c r="F216" t="n">
-        <v>0</v>
-      </c>
-      <c r="G216" t="n">
-        <v>1</v>
-      </c>
-      <c r="H216" t="n">
-        <v>1</v>
-      </c>
-      <c r="I216" t="n">
-        <v>0</v>
-      </c>
-      <c r="J216" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" t="n">
-        <v>4</v>
-      </c>
-      <c r="L216" t="n">
-        <v>2</v>
-      </c>
-      <c r="M216" t="n">
-        <v>1</v>
-      </c>
-      <c r="N216" t="n">
-        <v>0</v>
-      </c>
-      <c r="O216" t="n">
-        <v>0</v>
-      </c>
-      <c r="P216" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>1</v>
-      </c>
-      <c r="R216" t="n">
-        <v>4</v>
-      </c>
-      <c r="S216" t="n">
-        <v>2</v>
-      </c>
-      <c r="T216" t="n">
-        <v>2</v>
-      </c>
-      <c r="U216" t="n">
-        <v>11.65100638977636</v>
-      </c>
-      <c r="V216" t="n">
-        <v>-3</v>
-      </c>
       <c r="W216" t="n">
-        <v>-17.16972843450479</v>
+        <v>23.56266666666667</v>
       </c>
     </row>
     <row r="217">
@@ -16678,53 +16678,53 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>D. SANADZE</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D217" t="n">
-        <v>29.75</v>
+        <v>26.05</v>
       </c>
       <c r="E217" t="n">
-        <v>1785</v>
+        <v>1563</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H217" t="n">
         <v>4</v>
       </c>
       <c r="I217" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J217" t="n">
         <v>2</v>
       </c>
       <c r="K217" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L217" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M217" t="n">
-        <v>0.3125</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N217" t="n">
         <v>0</v>
       </c>
       <c r="O217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P217" t="n">
         <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
         <v>1</v>
@@ -16736,13 +16736,13 @@
         <v>1</v>
       </c>
       <c r="U217" t="n">
-        <v>33.02285042016807</v>
+        <v>49.98703646833013</v>
       </c>
       <c r="V217" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="W217" t="n">
-        <v>-42.30749579831933</v>
+        <v>-40.98514011516315</v>
       </c>
     </row>
     <row r="218">
@@ -16753,26 +16753,26 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>I. MASSOUD RODRÍGUEZ</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D218" t="n">
-        <v>1.73</v>
+        <v>12.52</v>
       </c>
       <c r="E218" t="n">
-        <v>103.8</v>
+        <v>751.2</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218" t="n">
         <v>0</v>
@@ -16781,13 +16781,13 @@
         <v>0</v>
       </c>
       <c r="K218" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N218" t="n">
         <v>0</v>
@@ -16799,25 +16799,25 @@
         <v>0</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U218" t="n">
-        <v>0</v>
+        <v>11.65100638977636</v>
       </c>
       <c r="V218" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="W218" t="n">
-        <v>-66.67</v>
+        <v>-17.16972843450479</v>
       </c>
     </row>
     <row r="219">
@@ -16828,71 +16828,71 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="C219" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D219" t="n">
-        <v>23.42</v>
+        <v>29.75</v>
       </c>
       <c r="E219" t="n">
-        <v>1405.2</v>
+        <v>1785</v>
       </c>
       <c r="F219" t="n">
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H219" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I219" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K219" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L219" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M219" t="n">
-        <v>0.875</v>
+        <v>0.3125</v>
       </c>
       <c r="N219" t="n">
         <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R219" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T219" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U219" t="n">
-        <v>16.12861656703672</v>
+        <v>33.02285042016807</v>
       </c>
       <c r="V219" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="W219" t="n">
-        <v>-31.40467549103331</v>
+        <v>-42.30749579831933</v>
       </c>
     </row>
     <row r="220">
@@ -16903,23 +16903,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>I. MASSOUD RODRÍGUEZ</t>
         </is>
       </c>
       <c r="C220" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>4.19</v>
+        <v>1.73</v>
       </c>
       <c r="E220" t="n">
-        <v>251.4</v>
+        <v>103.8</v>
       </c>
       <c r="F220" t="n">
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -16961,13 +16961,13 @@
         <v>0</v>
       </c>
       <c r="U220" t="n">
-        <v>42.92992840095465</v>
+        <v>0</v>
       </c>
       <c r="V220" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="W220" t="n">
-        <v>-88.64847255369929</v>
+        <v>-66.67</v>
       </c>
     </row>
     <row r="221">
@@ -16978,47 +16978,47 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D221" t="n">
-        <v>6.630000000000001</v>
+        <v>23.42</v>
       </c>
       <c r="E221" t="n">
-        <v>397.8</v>
+        <v>1405.2</v>
       </c>
       <c r="F221" t="n">
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H221" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M221" t="n">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
       <c r="N221" t="n">
         <v>0</v>
       </c>
       <c r="O221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P221" t="n">
         <v>1</v>
@@ -17027,22 +17027,22 @@
         <v>0</v>
       </c>
       <c r="R221" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U221" t="n">
-        <v>34.73858220211162</v>
+        <v>16.12861656703672</v>
       </c>
       <c r="V221" t="n">
-        <v>10</v>
+        <v>-4</v>
       </c>
       <c r="W221" t="n">
-        <v>45.56488687782805</v>
+        <v>-31.40467549103331</v>
       </c>
     </row>
     <row r="222">
@@ -17053,41 +17053,41 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D222" t="n">
-        <v>22.24</v>
+        <v>4.19</v>
       </c>
       <c r="E222" t="n">
-        <v>1334.4</v>
+        <v>251.4</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H222" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="N222" t="n">
         <v>0</v>
@@ -17096,28 +17096,28 @@
         <v>0</v>
       </c>
       <c r="P222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R222" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S222" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T222" t="n">
         <v>0</v>
       </c>
       <c r="U222" t="n">
-        <v>22.0836690647482</v>
+        <v>42.92992840095465</v>
       </c>
       <c r="V222" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="W222" t="n">
-        <v>-30.44895683453237</v>
+        <v>-88.64847255369929</v>
       </c>
     </row>
     <row r="223">
@@ -17128,116 +17128,116 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>P. SCRUBB</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="C223" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D223" t="n">
-        <v>25.06</v>
+        <v>6.630000000000001</v>
       </c>
       <c r="E223" t="n">
-        <v>1503.6</v>
+        <v>397.8</v>
       </c>
       <c r="F223" t="n">
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H223" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.5</v>
       </c>
       <c r="N223" t="n">
         <v>0</v>
       </c>
       <c r="O223" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q223" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R223" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S223" t="n">
         <v>1</v>
       </c>
       <c r="T223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U223" t="n">
-        <v>41.79373104549082</v>
+        <v>34.73858220211162</v>
       </c>
       <c r="V223" t="n">
-        <v>-12</v>
+        <v>10</v>
       </c>
       <c r="W223" t="n">
-        <v>-56.26701915403032</v>
+        <v>45.56488687782805</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
+          <t>PALMER BASKET MALLORCA PALMA</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="C224" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D224" t="n">
-        <v>5.88</v>
+        <v>22.24</v>
       </c>
       <c r="E224" t="n">
-        <v>352.8</v>
+        <v>1334.4</v>
       </c>
       <c r="F224" t="n">
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H224" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="N224" t="n">
         <v>0</v>
@@ -17246,85 +17246,85 @@
         <v>0</v>
       </c>
       <c r="P224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R224" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S224" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T224" t="n">
         <v>0</v>
       </c>
       <c r="U224" t="n">
-        <v>43.73086734693877</v>
+        <v>22.0836690647482</v>
       </c>
       <c r="V224" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W224" t="n">
-        <v>37.91649659863945</v>
+        <v>-30.44895683453237</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SÚPER AGROPAL PALENCIA</t>
+          <t>PALMER BASKET MALLORCA PALMA</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>P. SCRUBB</t>
         </is>
       </c>
       <c r="C225" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D225" t="n">
-        <v>3.02</v>
+        <v>25.06</v>
       </c>
       <c r="E225" t="n">
-        <v>181.2</v>
+        <v>1503.6</v>
       </c>
       <c r="F225" t="n">
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H225" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I225" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K225" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="N225" t="n">
         <v>0</v>
       </c>
       <c r="O225" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P225" t="n">
         <v>0</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R225" t="n">
         <v>2</v>
@@ -17336,13 +17336,13 @@
         <v>1</v>
       </c>
       <c r="U225" t="n">
-        <v>76.76006622516557</v>
+        <v>41.79373104549082</v>
       </c>
       <c r="V225" t="n">
-        <v>7</v>
+        <v>-12</v>
       </c>
       <c r="W225" t="n">
-        <v>132.4503311258278</v>
+        <v>-56.26701915403032</v>
       </c>
     </row>
     <row r="226">
@@ -17353,47 +17353,47 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="C226" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D226" t="n">
-        <v>11.62</v>
+        <v>5.88</v>
       </c>
       <c r="E226" t="n">
-        <v>697.2</v>
+        <v>352.8</v>
       </c>
       <c r="F226" t="n">
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H226" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K226" t="n">
         <v>2</v>
       </c>
       <c r="L226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M226" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.75</v>
       </c>
       <c r="N226" t="n">
         <v>0</v>
       </c>
       <c r="O226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P226" t="n">
         <v>0</v>
@@ -17402,22 +17402,22 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S226" t="n">
         <v>0</v>
       </c>
       <c r="T226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U226" t="n">
-        <v>30.67005163511188</v>
+        <v>43.73086734693877</v>
       </c>
       <c r="V226" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="W226" t="n">
-        <v>124.8553700516351</v>
+        <v>37.91649659863945</v>
       </c>
     </row>
     <row r="227">
@@ -17428,17 +17428,17 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="C227" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D227" t="n">
-        <v>10.62</v>
+        <v>3.02</v>
       </c>
       <c r="E227" t="n">
-        <v>637.2</v>
+        <v>181.2</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -17447,28 +17447,28 @@
         <v>2</v>
       </c>
       <c r="H227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I227" t="n">
         <v>2</v>
       </c>
       <c r="J227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K227" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L227" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M227" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="N227" t="n">
         <v>0</v>
       </c>
       <c r="O227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P227" t="n">
         <v>0</v>
@@ -17477,22 +17477,22 @@
         <v>0</v>
       </c>
       <c r="R227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T227" t="n">
         <v>1</v>
       </c>
       <c r="U227" t="n">
-        <v>20.54084745762711</v>
+        <v>76.76006622516557</v>
       </c>
       <c r="V227" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W227" t="n">
-        <v>46.21562146892655</v>
+        <v>132.4503311258278</v>
       </c>
     </row>
     <row r="228">
@@ -17503,41 +17503,41 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="C228" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D228" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="E228" t="n">
+        <v>996</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
         <v>9</v>
       </c>
-      <c r="E228" t="n">
-        <v>540</v>
-      </c>
-      <c r="F228" t="n">
-        <v>0</v>
-      </c>
-      <c r="G228" t="n">
-        <v>3</v>
-      </c>
       <c r="H228" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I228" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L228" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M228" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="N228" t="n">
         <v>0</v>
@@ -17552,22 +17552,22 @@
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T228" t="n">
         <v>1</v>
       </c>
       <c r="U228" t="n">
-        <v>27.9813</v>
+        <v>29.41003614457831</v>
       </c>
       <c r="V228" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="W228" t="n">
-        <v>72.78034444444444</v>
+        <v>87.94175903614456</v>
       </c>
     </row>
     <row r="229">
@@ -17578,38 +17578,38 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="C229" t="n">
+        <v>4</v>
+      </c>
+      <c r="D229" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="E229" t="n">
+        <v>637.2</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>2</v>
+      </c>
+      <c r="H229" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" t="n">
+        <v>2</v>
+      </c>
+      <c r="J229" t="n">
+        <v>1</v>
+      </c>
+      <c r="K229" t="n">
+        <v>6</v>
+      </c>
+      <c r="L229" t="n">
         <v>5</v>
-      </c>
-      <c r="D229" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="E229" t="n">
-        <v>561.6</v>
-      </c>
-      <c r="F229" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" t="n">
-        <v>4</v>
-      </c>
-      <c r="H229" t="n">
-        <v>3</v>
-      </c>
-      <c r="I229" t="n">
-        <v>0</v>
-      </c>
-      <c r="J229" t="n">
-        <v>0</v>
-      </c>
-      <c r="K229" t="n">
-        <v>0</v>
-      </c>
-      <c r="L229" t="n">
-        <v>0</v>
       </c>
       <c r="M229" t="n">
         <v>0.75</v>
@@ -17618,31 +17618,31 @@
         <v>0</v>
       </c>
       <c r="O229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P229" t="n">
         <v>0</v>
       </c>
       <c r="Q229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U229" t="n">
-        <v>28.84116452991453</v>
+        <v>20.54084745762711</v>
       </c>
       <c r="V229" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="W229" t="n">
-        <v>126.7211752136752</v>
+        <v>46.21562146892655</v>
       </c>
     </row>
     <row r="230">
@@ -17653,47 +17653,47 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="C230" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D230" t="n">
-        <v>6.289999999999999</v>
+        <v>13.98</v>
       </c>
       <c r="E230" t="n">
-        <v>377.4</v>
+        <v>838.8</v>
       </c>
       <c r="F230" t="n">
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I230" t="n">
         <v>1</v>
       </c>
       <c r="J230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M230" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="N230" t="n">
         <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P230" t="n">
         <v>0</v>
@@ -17702,22 +17702,22 @@
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U230" t="n">
-        <v>10.59777424483307</v>
+        <v>24.56109442060086</v>
       </c>
       <c r="V230" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W230" t="n">
-        <v>143.3685691573927</v>
+        <v>47.49906294706724</v>
       </c>
     </row>
     <row r="231">
@@ -17728,26 +17728,26 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>S. UGOCHUKWU</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="C231" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D231" t="n">
-        <v>3.45</v>
+        <v>10.33</v>
       </c>
       <c r="E231" t="n">
-        <v>207</v>
+        <v>619.8000000000001</v>
       </c>
       <c r="F231" t="n">
         <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -17762,7 +17762,7 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N231" t="n">
         <v>0</v>
@@ -17774,25 +17774,25 @@
         <v>0</v>
       </c>
       <c r="Q231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R231" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T231" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U231" t="n">
-        <v>31.88405797101449</v>
+        <v>26.13294288480154</v>
       </c>
       <c r="V231" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="W231" t="n">
-        <v>-22.37231884057972</v>
+        <v>105.4317715392062</v>
       </c>
     </row>
     <row r="232">
@@ -17803,71 +17803,71 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D232" t="n">
-        <v>11.15</v>
+        <v>10.47</v>
       </c>
       <c r="E232" t="n">
-        <v>669</v>
+        <v>628.1999999999999</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J232" t="n">
         <v>1</v>
       </c>
       <c r="K232" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>0.375</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N232" t="n">
         <v>0</v>
       </c>
       <c r="O232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q232" t="n">
         <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S232" t="n">
         <v>1</v>
       </c>
       <c r="T232" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U232" t="n">
-        <v>32.88670852017937</v>
+        <v>19.85295128939828</v>
       </c>
       <c r="V232" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W232" t="n">
-        <v>76.14411659192825</v>
+        <v>96.3750811843362</v>
       </c>
     </row>
     <row r="233">
@@ -17878,71 +17878,296 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
+          <t>S. UGOCHUKWU</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>2</v>
+      </c>
+      <c r="D233" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="E233" t="n">
+        <v>207</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>1</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="n">
+        <v>0</v>
+      </c>
+      <c r="R233" t="n">
+        <v>2</v>
+      </c>
+      <c r="S233" t="n">
+        <v>1</v>
+      </c>
+      <c r="T233" t="n">
+        <v>1</v>
+      </c>
+      <c r="U233" t="n">
+        <v>31.88405797101449</v>
+      </c>
+      <c r="V233" t="n">
+        <v>4</v>
+      </c>
+      <c r="W233" t="n">
+        <v>-22.37231884057972</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>T. BORG</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>7</v>
+      </c>
+      <c r="D234" t="n">
+        <v>16.13</v>
+      </c>
+      <c r="E234" t="n">
+        <v>967.8</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="n">
+        <v>5</v>
+      </c>
+      <c r="H234" t="n">
+        <v>2</v>
+      </c>
+      <c r="I234" t="n">
+        <v>4</v>
+      </c>
+      <c r="J234" t="n">
+        <v>2</v>
+      </c>
+      <c r="K234" t="n">
+        <v>3</v>
+      </c>
+      <c r="L234" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>2</v>
+      </c>
+      <c r="P234" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q234" t="n">
+        <v>1</v>
+      </c>
+      <c r="R234" t="n">
+        <v>1</v>
+      </c>
+      <c r="S234" t="n">
+        <v>1</v>
+      </c>
+      <c r="T234" t="n">
+        <v>0</v>
+      </c>
+      <c r="U234" t="n">
+        <v>28.40788592684439</v>
+      </c>
+      <c r="V234" t="n">
+        <v>15</v>
+      </c>
+      <c r="W234" t="n">
+        <v>53.19409175449474</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>V. VUCETIC</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="E235" t="n">
+        <v>241.2</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0</v>
+      </c>
+      <c r="G235" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>0</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q235" t="n">
+        <v>0</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0</v>
+      </c>
+      <c r="S235" t="n">
+        <v>0</v>
+      </c>
+      <c r="T235" t="n">
+        <v>0</v>
+      </c>
+      <c r="U235" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="V235" t="n">
+        <v>3</v>
+      </c>
+      <c r="W235" t="n">
+        <v>25.66</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>SÚPER AGROPAL PALENCIA</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
           <t>X. OROZ URIA</t>
         </is>
       </c>
-      <c r="C233" t="n">
-        <v>2</v>
-      </c>
-      <c r="D233" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E233" t="n">
-        <v>132</v>
-      </c>
-      <c r="F233" t="n">
-        <v>0</v>
-      </c>
-      <c r="G233" t="n">
-        <v>2</v>
-      </c>
-      <c r="H233" t="n">
-        <v>1</v>
-      </c>
-      <c r="I233" t="n">
-        <v>0</v>
-      </c>
-      <c r="J233" t="n">
-        <v>0</v>
-      </c>
-      <c r="K233" t="n">
-        <v>0</v>
-      </c>
-      <c r="L233" t="n">
-        <v>0</v>
-      </c>
-      <c r="M233" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N233" t="n">
-        <v>0</v>
-      </c>
-      <c r="O233" t="n">
-        <v>0</v>
-      </c>
-      <c r="P233" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
-      <c r="R233" t="n">
-        <v>0</v>
-      </c>
-      <c r="S233" t="n">
-        <v>0</v>
-      </c>
-      <c r="T233" t="n">
-        <v>0</v>
-      </c>
-      <c r="U233" t="n">
-        <v>31.66636363636364</v>
-      </c>
-      <c r="V233" t="n">
-        <v>8</v>
-      </c>
-      <c r="W233" t="n">
-        <v>119.1840909090909</v>
+      <c r="C236" t="n">
+        <v>3</v>
+      </c>
+      <c r="D236" t="n">
+        <v>3</v>
+      </c>
+      <c r="E236" t="n">
+        <v>180</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="n">
+        <v>3</v>
+      </c>
+      <c r="H236" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" t="n">
+        <v>1</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q236" t="n">
+        <v>0</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0</v>
+      </c>
+      <c r="S236" t="n">
+        <v>0</v>
+      </c>
+      <c r="T236" t="n">
+        <v>0</v>
+      </c>
+      <c r="U236" t="n">
+        <v>36.55533333333334</v>
+      </c>
+      <c r="V236" t="n">
+        <v>6</v>
+      </c>
+      <c r="W236" t="n">
+        <v>60.735</v>
       </c>
     </row>
   </sheetData>

--- a/data/1FEB_25_26/clutch_aggregated_25_26_1FEB.xlsx
+++ b/data/1FEB_25_26/clutch_aggregated_25_26_1FEB.xlsx
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>22.52</v>
+        <v>22.89</v>
       </c>
       <c r="E2" t="n">
-        <v>1351.2</v>
+        <v>1373.4</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -611,13 +611,13 @@
         <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>14.9045026642984</v>
+        <v>14.66358235037134</v>
       </c>
       <c r="V2" t="n">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6147957371225573</v>
+        <v>-2.221284403669724</v>
       </c>
     </row>
     <row r="3">
@@ -707,25 +707,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>19.81</v>
+        <v>24.51</v>
       </c>
       <c r="E4" t="n">
-        <v>1188.6</v>
+        <v>1470.6</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -737,13 +737,13 @@
         <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.375</v>
+        <v>0.3</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -761,13 +761,13 @@
         <v>3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.16330641090358</v>
+        <v>19.13292941656466</v>
       </c>
       <c r="V4" t="n">
         <v>-7</v>
       </c>
       <c r="W4" t="n">
-        <v>-7.023528520949016</v>
+        <v>-1.27968584251326</v>
       </c>
     </row>
     <row r="5">
@@ -932,25 +932,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>40.17</v>
+        <v>44.87</v>
       </c>
       <c r="E7" t="n">
-        <v>2410.2</v>
+        <v>2692.2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
         <v>2</v>
@@ -962,7 +962,7 @@
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -977,22 +977,22 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
         <v>8</v>
       </c>
       <c r="U7" t="n">
-        <v>20.31510082150859</v>
+        <v>19.73636282594161</v>
       </c>
       <c r="V7" t="n">
         <v>-3</v>
       </c>
       <c r="W7" t="n">
-        <v>5.355354742345035</v>
+        <v>7.196246935591711</v>
       </c>
     </row>
     <row r="8">
@@ -1157,37 +1157,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>36.41</v>
+        <v>41.11</v>
       </c>
       <c r="E10" t="n">
-        <v>2184.6</v>
+        <v>2466.6</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
+        <v>19</v>
+      </c>
+      <c r="L10" t="n">
         <v>17</v>
       </c>
-      <c r="L10" t="n">
-        <v>16</v>
-      </c>
       <c r="M10" t="n">
-        <v>0.32</v>
+        <v>0.3103448275862069</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1202,22 +1202,22 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>62.35842351002474</v>
+        <v>63.48244222816834</v>
       </c>
       <c r="V10" t="n">
         <v>-2</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.9339686899203524</v>
+        <v>1.794337144247141</v>
       </c>
     </row>
     <row r="11">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>25.79</v>
+        <v>30.12</v>
       </c>
       <c r="E12" t="n">
-        <v>1547.4</v>
+        <v>1807.2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1331,10 +1331,10 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
         <v>0.8</v>
@@ -1352,22 +1352,22 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
         <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>12.95260566110896</v>
+        <v>13.28718791500664</v>
       </c>
       <c r="V12" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="W12" t="n">
-        <v>-33.5263823187282</v>
+        <v>-22.91610225763613</v>
       </c>
     </row>
     <row r="13">
@@ -1382,28 +1382,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>44.89</v>
+        <v>49.59</v>
       </c>
       <c r="E13" t="n">
-        <v>2693.4</v>
+        <v>2975.4</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
@@ -1412,7 +1412,7 @@
         <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>0.75</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1427,22 +1427,22 @@
         <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>25.17963911784362</v>
+        <v>25.59764065335754</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>7.059685898863886</v>
+        <v>8.563829401088926</v>
       </c>
     </row>
     <row r="14">
@@ -2432,13 +2432,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" t="n">
-        <v>0.53</v>
+        <v>2.05</v>
       </c>
       <c r="E27" t="n">
-        <v>31.8</v>
+        <v>123</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W27" t="n">
-        <v>-71.69811320754717</v>
+        <v>-78.71375609756099</v>
       </c>
     </row>
     <row r="28">
@@ -2507,22 +2507,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="E28" t="n">
-        <v>408</v>
+        <v>690</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2561,13 +2561,13 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>26.52155882352941</v>
+        <v>25.89970434782609</v>
       </c>
       <c r="V28" t="n">
         <v>-8</v>
       </c>
       <c r="W28" t="n">
-        <v>-163.0636617647058</v>
+        <v>-105.7916434782609</v>
       </c>
     </row>
     <row r="29">
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>13</v>
+      </c>
+      <c r="D30" t="n">
+        <v>37.87</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2272.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>12</v>
-      </c>
-      <c r="D30" t="n">
-        <v>34.69</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2081.4</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>11</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -2687,7 +2687,7 @@
         <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
@@ -2711,13 +2711,13 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>30.09992216777169</v>
+        <v>29.67167414840243</v>
       </c>
       <c r="V30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>-5.448466416834818</v>
+        <v>-2.891663585951937</v>
       </c>
     </row>
     <row r="31">
@@ -2732,44 +2732,44 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D31" t="n">
-        <v>26.96</v>
+        <v>31.66</v>
       </c>
       <c r="E31" t="n">
-        <v>1617.6</v>
+        <v>1899.6</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H31" t="n">
         <v>6</v>
       </c>
       <c r="I31" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>6</v>
       </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>4</v>
-      </c>
       <c r="P31" t="n">
         <v>1</v>
       </c>
@@ -2777,22 +2777,22 @@
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U31" t="n">
-        <v>46.97092729970326</v>
+        <v>41.85363866077068</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>-15.55140207715134</v>
+        <v>-16.64677195198989</v>
       </c>
     </row>
     <row r="32">
@@ -2882,67 +2882,67 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="E33" t="n">
+        <v>732.6</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
         <v>5</v>
       </c>
-      <c r="D33" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="E33" t="n">
-        <v>450.6</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>4</v>
-      </c>
       <c r="S33" t="n">
         <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U33" t="n">
-        <v>69.36014647137151</v>
+        <v>57.09620802620803</v>
       </c>
       <c r="V33" t="n">
         <v>3</v>
       </c>
       <c r="W33" t="n">
-        <v>64.70936085219707</v>
+        <v>30.97430794430795</v>
       </c>
     </row>
     <row r="34">
@@ -3257,67 +3257,67 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>31.27</v>
+        <v>35.97</v>
       </c>
       <c r="E38" t="n">
-        <v>1876.2</v>
+        <v>2158.2</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
+        <v>11</v>
+      </c>
+      <c r="H38" t="n">
+        <v>9</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>14</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6</v>
+      </c>
+      <c r="T38" t="n">
         <v>8</v>
       </c>
-      <c r="H38" t="n">
-        <v>7</v>
-      </c>
-      <c r="I38" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2</v>
-      </c>
-      <c r="L38" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2</v>
-      </c>
-      <c r="R38" t="n">
-        <v>11</v>
-      </c>
-      <c r="S38" t="n">
-        <v>5</v>
-      </c>
-      <c r="T38" t="n">
-        <v>6</v>
-      </c>
       <c r="U38" t="n">
-        <v>13.74765909817717</v>
+        <v>16.8512454823464</v>
       </c>
       <c r="V38" t="n">
         <v>11</v>
       </c>
       <c r="W38" t="n">
-        <v>27.5089958426607</v>
+        <v>20.91841256602725</v>
       </c>
     </row>
     <row r="39">
@@ -5207,22 +5207,22 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D64" t="n">
-        <v>18.36</v>
+        <v>20.43</v>
       </c>
       <c r="E64" t="n">
-        <v>1101.6</v>
+        <v>1225.8</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -5243,7 +5243,7 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
@@ -5261,13 +5261,13 @@
         <v>4</v>
       </c>
       <c r="U64" t="n">
-        <v>25.02211328976034</v>
+        <v>29.24194322075379</v>
       </c>
       <c r="V64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="W64" t="n">
-        <v>79.27154684095861</v>
+        <v>71.85363680861478</v>
       </c>
     </row>
     <row r="65">
@@ -5357,13 +5357,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D66" t="n">
-        <v>27</v>
+        <v>27.08</v>
       </c>
       <c r="E66" t="n">
-        <v>1620</v>
+        <v>1624.8</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -5411,13 +5411,13 @@
         <v>5</v>
       </c>
       <c r="U66" t="n">
-        <v>17.96831111111111</v>
+        <v>17.91522895125554</v>
       </c>
       <c r="V66" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="W66" t="n">
-        <v>93.39345185185185</v>
+        <v>93.11754800590842</v>
       </c>
     </row>
     <row r="67">
@@ -5432,13 +5432,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D67" t="n">
-        <v>17.88</v>
+        <v>19.95</v>
       </c>
       <c r="E67" t="n">
-        <v>1072.8</v>
+        <v>1197</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P67" t="n">
         <v>1</v>
@@ -5486,13 +5486,13 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>16.95011744966443</v>
+        <v>15.19138345864662</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="W67" t="n">
-        <v>-18.90921700223714</v>
+        <v>-16.31842606516291</v>
       </c>
     </row>
     <row r="68">
@@ -5582,13 +5582,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D69" t="n">
-        <v>12.84</v>
+        <v>12.92</v>
       </c>
       <c r="E69" t="n">
-        <v>770.4</v>
+        <v>775.1999999999999</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -5636,13 +5636,13 @@
         <v>3</v>
       </c>
       <c r="U69" t="n">
-        <v>14.92002336448598</v>
+        <v>14.82763931888545</v>
       </c>
       <c r="V69" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W69" t="n">
-        <v>23.99939252336448</v>
+        <v>23.85078947368421</v>
       </c>
     </row>
     <row r="70">
@@ -5657,22 +5657,22 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D70" t="n">
-        <v>19.82</v>
+        <v>21.8</v>
       </c>
       <c r="E70" t="n">
-        <v>1189.2</v>
+        <v>1308</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
+        <v>6</v>
+      </c>
+      <c r="H70" t="n">
         <v>5</v>
-      </c>
-      <c r="H70" t="n">
-        <v>4</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -5687,7 +5687,7 @@
         <v>8</v>
       </c>
       <c r="M70" t="n">
-        <v>0.8</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N70" t="n">
         <v>0</v>
@@ -5702,22 +5702,22 @@
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
         <v>5</v>
       </c>
       <c r="U70" t="n">
-        <v>30.28271442986882</v>
+        <v>32.07355045871559</v>
       </c>
       <c r="V70" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W70" t="n">
-        <v>63.77890010090817</v>
+        <v>55.50932110091743</v>
       </c>
     </row>
     <row r="71">
@@ -5807,28 +5807,28 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>4.13</v>
+        <v>6.199999999999999</v>
       </c>
       <c r="E72" t="n">
-        <v>247.8</v>
+        <v>372</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -5837,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -5861,13 +5861,13 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>21.13133171912833</v>
+        <v>25.20411290322581</v>
       </c>
       <c r="V72" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="W72" t="n">
-        <v>-91.80847457627119</v>
+        <v>-59.13303225806453</v>
       </c>
     </row>
     <row r="73">
@@ -6032,25 +6032,25 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D75" t="n">
-        <v>22.15</v>
+        <v>24.13</v>
       </c>
       <c r="E75" t="n">
-        <v>1329</v>
+        <v>1447.8</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H75" t="n">
         <v>4</v>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J75" t="n">
         <v>1</v>
@@ -6062,7 +6062,7 @@
         <v>6</v>
       </c>
       <c r="M75" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.3214285714285715</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -6077,22 +6077,22 @@
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75" t="n">
         <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>48.37629796839729</v>
+        <v>48.50953170327394</v>
       </c>
       <c r="V75" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="W75" t="n">
-        <v>27.98348081264108</v>
+        <v>23.44962702030668</v>
       </c>
     </row>
     <row r="76">
@@ -15557,13 +15557,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D202" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="E202" t="n">
-        <v>144</v>
+        <v>148.8</v>
       </c>
       <c r="F202" t="n">
         <v>0</v>
@@ -15614,10 +15614,10 @@
         <v>0</v>
       </c>
       <c r="V202" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W202" t="n">
-        <v>-5.870416666666665</v>
+        <v>-5.681048387096772</v>
       </c>
     </row>
     <row r="203">
@@ -15707,13 +15707,13 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D204" t="n">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="E204" t="n">
-        <v>118.8</v>
+        <v>153.6</v>
       </c>
       <c r="F204" t="n">
         <v>0</v>
@@ -15761,13 +15761,13 @@
         <v>1</v>
       </c>
       <c r="U204" t="n">
-        <v>22.68</v>
+        <v>17.5415625</v>
       </c>
       <c r="V204" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="W204" t="n">
-        <v>-40.97999999999999</v>
+        <v>-31.69546875</v>
       </c>
     </row>
     <row r="205">
@@ -15782,13 +15782,13 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D205" t="n">
-        <v>35.09</v>
+        <v>37.16</v>
       </c>
       <c r="E205" t="n">
-        <v>2105.4</v>
+        <v>2229.6</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
@@ -15806,10 +15806,10 @@
         <v>0</v>
       </c>
       <c r="K205" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L205" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M205" t="n">
         <v>0.1538461538461539</v>
@@ -15836,13 +15836,13 @@
         <v>5</v>
       </c>
       <c r="U205" t="n">
-        <v>49.45485893416929</v>
+        <v>48.09259956942951</v>
       </c>
       <c r="V205" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="W205" t="n">
-        <v>-30.82259618124822</v>
+        <v>-29.4431942949408</v>
       </c>
     </row>
     <row r="206">
@@ -16082,13 +16082,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D209" t="n">
-        <v>2.03</v>
+        <v>3.43</v>
       </c>
       <c r="E209" t="n">
-        <v>121.8</v>
+        <v>205.8</v>
       </c>
       <c r="F209" t="n">
         <v>0</v>
@@ -16136,13 +16136,13 @@
         <v>0</v>
       </c>
       <c r="U209" t="n">
-        <v>32.15448275862069</v>
+        <v>19.03020408163265</v>
       </c>
       <c r="V209" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="W209" t="n">
-        <v>30.10778325123152</v>
+        <v>28.94950437317784</v>
       </c>
     </row>
     <row r="210">
@@ -16157,25 +16157,25 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D210" t="n">
-        <v>12.82</v>
+        <v>14.89</v>
       </c>
       <c r="E210" t="n">
-        <v>769.2</v>
+        <v>893.4</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H210" t="n">
         <v>3</v>
       </c>
       <c r="I210" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J210" t="n">
         <v>1</v>
@@ -16187,7 +16187,7 @@
         <v>3</v>
       </c>
       <c r="M210" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5</v>
       </c>
       <c r="N210" t="n">
         <v>0</v>
@@ -16202,22 +16202,22 @@
         <v>2</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T210" t="n">
         <v>0</v>
       </c>
       <c r="U210" t="n">
-        <v>30.49762090483619</v>
+        <v>30.20740094022834</v>
       </c>
       <c r="V210" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="W210" t="n">
-        <v>-49.04762870514821</v>
+        <v>-43.07151108126259</v>
       </c>
     </row>
     <row r="211">
@@ -16307,13 +16307,13 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D212" t="n">
-        <v>1.51</v>
+        <v>3.58</v>
       </c>
       <c r="E212" t="n">
-        <v>90.59999999999999</v>
+        <v>214.8</v>
       </c>
       <c r="F212" t="n">
         <v>0</v>
@@ -16331,10 +16331,10 @@
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M212" t="n">
         <v>1</v>
@@ -16361,13 +16361,13 @@
         <v>0</v>
       </c>
       <c r="U212" t="n">
-        <v>14.34735099337748</v>
+        <v>20.50684357541899</v>
       </c>
       <c r="V212" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="W212" t="n">
-        <v>-10.90013245033112</v>
+        <v>-8.101508379888267</v>
       </c>
     </row>
     <row r="213">
@@ -16382,13 +16382,13 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D213" t="n">
-        <v>11.57</v>
+        <v>12.97</v>
       </c>
       <c r="E213" t="n">
-        <v>694.2</v>
+        <v>778.2</v>
       </c>
       <c r="F213" t="n">
         <v>0</v>
@@ -16406,10 +16406,10 @@
         <v>0</v>
       </c>
       <c r="K213" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L213" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
@@ -16436,13 +16436,13 @@
         <v>1</v>
       </c>
       <c r="U213" t="n">
-        <v>19.7200691443388</v>
+        <v>24.78791056283731</v>
       </c>
       <c r="V213" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="W213" t="n">
-        <v>29.02229040622299</v>
+        <v>28.83314572089437</v>
       </c>
     </row>
     <row r="214">
@@ -16457,13 +16457,13 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D214" t="n">
-        <v>24.71</v>
+        <v>24.79</v>
       </c>
       <c r="E214" t="n">
-        <v>1482.6</v>
+        <v>1487.4</v>
       </c>
       <c r="F214" t="n">
         <v>0</v>
@@ -16511,13 +16511,13 @@
         <v>1</v>
       </c>
       <c r="U214" t="n">
-        <v>11.60048968029138</v>
+        <v>11.56305365066559</v>
       </c>
       <c r="V214" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="W214" t="n">
-        <v>-11.7873452043707</v>
+        <v>-11.74930617184348</v>
       </c>
     </row>
     <row r="215">
